--- a/graduation-api/convidados_confirmados.xlsx
+++ b/graduation-api/convidados_confirmados.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,114 +430,159 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Carlos Anderson Vargas da Silva</v>
+        <v>Lucas Silva</v>
       </c>
       <c r="C2" t="str">
-        <v>CRIANCA (40 anos)</v>
-      </c>
-      <c r="D2">
-        <v>40</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2">
-        <v>1240</v>
+        <v>3261</v>
       </c>
       <c r="F2" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G2" t="str">
-        <v>19/04/2025</v>
+        <v>20/04/2025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Benjamin Silva</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3">
+        <v>3261</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G3" t="str">
+        <v>20/04/2025</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Sabrina Roani</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4">
+        <v>3261</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G4" t="str">
+        <v>20/04/2025</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>João Batista</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5">
+        <v>3261</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G5" t="str">
+        <v>20/04/2025</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Benicio Silva</v>
+      </c>
+      <c r="C6" t="str">
+        <v>CRIANCA (5 anos)</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>3261</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G6" t="str">
+        <v>20/04/2025</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Joaquim Silva</v>
+      </c>
+      <c r="C7" t="str">
+        <v>CRIANCA (10 anos)</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>3261</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G7" t="str">
+        <v>20/04/2025</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>#</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Nome</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Tipo</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Idade</v>
-      </c>
-      <c r="E1" t="str">
-        <v>CodigoConvite</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="G1" t="str">
-        <v>DataConfirmacao</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>João Pedro Vargas da Silva</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2">
-        <v>1240</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Recusado</v>
-      </c>
-      <c r="G2" t="str">
-        <v>19/04/2025</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Andreia Silva da Silva</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3">
-        <v>1240</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Recusado</v>
-      </c>
-      <c r="G3" t="str">
-        <v>19/04/2025</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G88"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -567,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Marcelo Vergara</v>
+        <v>João Pedro Silva</v>
       </c>
       <c r="C2" t="str">
         <v>Adulto</v>
@@ -576,7 +621,7 @@
         <v/>
       </c>
       <c r="E2">
-        <v>8228</v>
+        <v>1240</v>
       </c>
       <c r="F2" t="str">
         <v>Pendente</v>
@@ -590,7 +635,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Caroline Farias</v>
+        <v>Carlos Silva</v>
       </c>
       <c r="C3" t="str">
         <v>Adulto</v>
@@ -599,7 +644,7 @@
         <v/>
       </c>
       <c r="E3">
-        <v>8228</v>
+        <v>1240</v>
       </c>
       <c r="F3" t="str">
         <v>Pendente</v>
@@ -613,7 +658,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Guilherme Mocelin</v>
+        <v>Andréia Silva</v>
       </c>
       <c r="C4" t="str">
         <v>Adulto</v>
@@ -622,13 +667,13 @@
         <v/>
       </c>
       <c r="E4">
-        <v>9871</v>
+        <v>1240</v>
       </c>
       <c r="F4" t="str">
         <v>Pendente</v>
       </c>
       <c r="G4" t="str">
-        <v>19/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -636,7 +681,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Lucas Silva</v>
+        <v>Sandra Silva</v>
       </c>
       <c r="C5" t="str">
         <v>Adulto</v>
@@ -645,7 +690,7 @@
         <v/>
       </c>
       <c r="E5">
-        <v>3261</v>
+        <v>6744</v>
       </c>
       <c r="F5" t="str">
         <v>Pendente</v>
@@ -659,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Sabrina Roani</v>
+        <v>Antônio Renê Silva</v>
       </c>
       <c r="C6" t="str">
         <v>Adulto</v>
@@ -668,7 +713,7 @@
         <v/>
       </c>
       <c r="E6">
-        <v>3261</v>
+        <v>6744</v>
       </c>
       <c r="F6" t="str">
         <v>Pendente</v>
@@ -682,16 +727,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Benjamin Silva</v>
+        <v>Nicole Silva</v>
       </c>
       <c r="C7" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7">
-        <v>3261</v>
+        <v>2580</v>
       </c>
       <c r="F7" t="str">
         <v>Pendente</v>
@@ -705,16 +750,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Benicio Silva</v>
+        <v>Pedro Tremarin</v>
       </c>
       <c r="C8" t="str">
-        <v>CRIANCA (9 anos)</v>
-      </c>
-      <c r="D8">
-        <v>9</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8">
-        <v>3261</v>
+        <v>2580</v>
       </c>
       <c r="F8" t="str">
         <v>Pendente</v>
@@ -728,27 +773,1844 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Joaquim Silva</v>
+        <v>João Paulo Silva</v>
       </c>
       <c r="C9" t="str">
-        <v>CRIANCA (3 anos)</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
       </c>
       <c r="E9">
-        <v>3261</v>
+        <v>4417</v>
       </c>
       <c r="F9" t="str">
         <v>Pendente</v>
       </c>
       <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Vanessa Brum</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10">
+        <v>4417</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Leonardo Brum</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11">
+        <v>4417</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Maria Silva</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>2550</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Ísis Silva</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13">
+        <v>6612</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Graça Silva</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14">
+        <v>1754</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Renato</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15">
+        <v>1754</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Cheila Machado</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16">
+        <v>5820</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Paulo Machado</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17">
+        <v>5820</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Gustavo Machado</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18">
+        <v>8262</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Yasmin Teixeira</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19">
+        <v>8262</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Arthur Machado</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20">
+        <v>4410</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Rafaella Buttenbender</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21">
+        <v>4410</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Nice</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22">
+        <v>2309</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Clemi</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23">
+        <v>1111</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Vilson</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24">
+        <v>7361</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Rita</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25">
+        <v>7361</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Rose</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26">
+        <v>1636</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Ronei</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27">
+        <v>1636</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Volmar Machado</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28">
+        <v>8234</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Lurdes</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29">
+        <v>2222</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Cecinha</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30">
+        <v>3333</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Claudete Freitas</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31">
+        <v>8990</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Elizabeth</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32">
+        <v>8990</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Lucas Garcia</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33">
+        <v>2558</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Monique</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34">
+        <v>2558</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Ivonete</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35">
+        <v>5555</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Einar Marques</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36">
+        <v>5496</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Fabiana Gomes</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37">
+        <v>5496</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Marco Martins</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38">
+        <v>5001</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Rose Tormann</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39">
+        <v>5001</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Júlio</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40">
+        <v>5124</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Jocasta</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41">
+        <v>5124</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Fábio</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42">
+        <v>9772</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Cleci</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43">
+        <v>9772</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Yasmin</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44">
+        <v>9772</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Paulete</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45">
+        <v>2978</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Isaura Monteiro</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46">
+        <v>4666</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Vanessa Kissler</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47">
+        <v>1228</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Guilherme Becker</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48">
+        <v>1228</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Maria Eduarda Rocha</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49">
+        <v>5690</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50">
+        <v>5690</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Ivan Pedro Freitas</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51">
+        <v>1001</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Erick Almeida</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52">
+        <v>9251</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Matheus</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53">
+        <v>9251</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Guilherme Mocelin</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54">
+        <v>9871</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Caroline Farias</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55">
+        <v>8228</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Marcelo Vergara</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56">
+        <v>8228</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Mateus Leote</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57">
+        <v>5990</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Julia Cardoso</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58">
+        <v>5990</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Sara Rubia</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59">
+        <v>8326</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Eduarda Leal</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60">
+        <v>3277</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Gabriela</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61">
+        <v>7792</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Eduardo Viegas</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62">
+        <v>5447</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Gabriele Knop</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63">
+        <v>5447</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Eduardo Kern</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64">
+        <v>8504</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Henrique Demarchi</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65">
+        <v>2036</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G65" t="str">
+        <v>19/04/2025</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Franciele de Leon</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66">
+        <v>8778</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Bruno Erling</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67">
+        <v>8778</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Sandriele de Leon</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68">
+        <v>4142</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Giuvanni Bagatini</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69">
+        <v>4142</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Rochele de Leon</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70">
+        <v>3163</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Sandro Marques</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71">
+        <v>3163</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Cleusa</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72">
+        <v>6684</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Luiz Airton</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73">
+        <v>6684</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Angela</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74">
+        <v>8602</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Alexandre</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75">
+        <v>8602</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Amanda</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76">
+        <v>1558</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G76" t="str">
+        <v>19/04/2025</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Giuliano</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77">
+        <v>1558</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G77" t="str">
+        <v>19/04/2025</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Natalia</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78">
+        <v>8602</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Guilherme Lobo</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79">
+        <v>8602</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Ana Paula Rangel</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80">
+        <v>9922</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Cesar Maia</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81">
+        <v>9922</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Daniel</v>
+      </c>
+      <c r="C82" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82">
+        <v>5124</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Lorenzo</v>
+      </c>
+      <c r="C83" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83">
+        <v>4142</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Julia</v>
+      </c>
+      <c r="C84" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84">
+        <v>5124</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Julia Erling</v>
+      </c>
+      <c r="C85" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85">
+        <v>8778</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Antonio</v>
+      </c>
+      <c r="C86" t="str">
+        <v>CRIANCA (5 anos)</v>
+      </c>
+      <c r="D86">
+        <v>5</v>
+      </c>
+      <c r="E86">
+        <v>1558</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G86" t="str">
+        <v>19/04/2025</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Theo</v>
+      </c>
+      <c r="C87" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87">
+        <v>8602</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Luisa Silva</v>
+      </c>
+      <c r="C88" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88">
+        <v>4417</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G88" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G88"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -782,25 +2644,25 @@
     </row>
     <row r="2">
       <c r="A2">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>87</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/graduation-api/convidados_confirmados.xlsx
+++ b/graduation-api/convidados_confirmados.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,7 +430,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Lucas Silva</v>
+        <v>João Pedro Silva</v>
       </c>
       <c r="C2" t="str">
         <v>Adulto</v>
@@ -439,13 +439,13 @@
         <v/>
       </c>
       <c r="E2">
-        <v>3261</v>
+        <v>1240</v>
       </c>
       <c r="F2" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G2" t="str">
-        <v>20/04/2025</v>
+        <v>14/05/2025</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Benjamin Silva</v>
+        <v>Carlos Silva</v>
       </c>
       <c r="C3" t="str">
         <v>Adulto</v>
@@ -462,13 +462,13 @@
         <v/>
       </c>
       <c r="E3">
-        <v>3261</v>
+        <v>1240</v>
       </c>
       <c r="F3" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G3" t="str">
-        <v>20/04/2025</v>
+        <v>14/05/2025</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Sabrina Roani</v>
+        <v>Andréia Silva</v>
       </c>
       <c r="C4" t="str">
         <v>Adulto</v>
@@ -485,13 +485,13 @@
         <v/>
       </c>
       <c r="E4">
-        <v>3261</v>
+        <v>1240</v>
       </c>
       <c r="F4" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G4" t="str">
-        <v>20/04/2025</v>
+        <v>14/05/2025</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>João Batista</v>
+        <v>Lucas Silva</v>
       </c>
       <c r="C5" t="str">
         <v>Adulto</v>
@@ -514,7 +514,7 @@
         <v>Confirmado</v>
       </c>
       <c r="G5" t="str">
-        <v>20/04/2025</v>
+        <v>13/05/2025</v>
       </c>
     </row>
     <row r="6">
@@ -522,13 +522,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Benicio Silva</v>
+        <v>Sabrina Roani</v>
       </c>
       <c r="C6" t="str">
-        <v>CRIANCA (5 anos)</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6">
         <v>3261</v>
@@ -537,7 +537,7 @@
         <v>Confirmado</v>
       </c>
       <c r="G6" t="str">
-        <v>20/04/2025</v>
+        <v>13/05/2025</v>
       </c>
     </row>
     <row r="7">
@@ -545,13 +545,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Joaquim Silva</v>
+        <v>João Batista</v>
       </c>
       <c r="C7" t="str">
-        <v>CRIANCA (10 anos)</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7">
         <v>3261</v>
@@ -560,12 +560,81 @@
         <v>Confirmado</v>
       </c>
       <c r="G7" t="str">
-        <v>20/04/2025</v>
+        <v>13/05/2025</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Benjamin Silva</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8">
+        <v>3261</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G8" t="str">
+        <v>13/05/2025</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Benicio Silva</v>
+      </c>
+      <c r="C9" t="str">
+        <v>CRIANCA (10 anos)</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>3261</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G9" t="str">
+        <v>13/05/2025</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Joaquim Silva</v>
+      </c>
+      <c r="C10" t="str">
+        <v>CRIANCA (8 anos)</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>3261</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G10" t="str">
+        <v>13/05/2025</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -612,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>João Pedro Silva</v>
+        <v>Sandra Silva</v>
       </c>
       <c r="C2" t="str">
         <v>Adulto</v>
@@ -621,7 +690,7 @@
         <v/>
       </c>
       <c r="E2">
-        <v>1240</v>
+        <v>6744</v>
       </c>
       <c r="F2" t="str">
         <v>Pendente</v>
@@ -635,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Carlos Silva</v>
+        <v>Antônio Renê Silva</v>
       </c>
       <c r="C3" t="str">
         <v>Adulto</v>
@@ -644,7 +713,7 @@
         <v/>
       </c>
       <c r="E3">
-        <v>1240</v>
+        <v>6744</v>
       </c>
       <c r="F3" t="str">
         <v>Pendente</v>
@@ -658,7 +727,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Andréia Silva</v>
+        <v>Nicole Silva</v>
       </c>
       <c r="C4" t="str">
         <v>Adulto</v>
@@ -667,7 +736,7 @@
         <v/>
       </c>
       <c r="E4">
-        <v>1240</v>
+        <v>2580</v>
       </c>
       <c r="F4" t="str">
         <v>Pendente</v>
@@ -681,7 +750,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Sandra Silva</v>
+        <v>Pedro Tremarin</v>
       </c>
       <c r="C5" t="str">
         <v>Adulto</v>
@@ -690,7 +759,7 @@
         <v/>
       </c>
       <c r="E5">
-        <v>6744</v>
+        <v>2580</v>
       </c>
       <c r="F5" t="str">
         <v>Pendente</v>
@@ -704,7 +773,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Antônio Renê Silva</v>
+        <v>João Paulo Silva</v>
       </c>
       <c r="C6" t="str">
         <v>Adulto</v>
@@ -713,7 +782,7 @@
         <v/>
       </c>
       <c r="E6">
-        <v>6744</v>
+        <v>4417</v>
       </c>
       <c r="F6" t="str">
         <v>Pendente</v>
@@ -727,7 +796,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Nicole Silva</v>
+        <v>Vanessa Brum</v>
       </c>
       <c r="C7" t="str">
         <v>Adulto</v>
@@ -736,7 +805,7 @@
         <v/>
       </c>
       <c r="E7">
-        <v>2580</v>
+        <v>4417</v>
       </c>
       <c r="F7" t="str">
         <v>Pendente</v>
@@ -750,7 +819,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Pedro Tremarin</v>
+        <v>Leonardo Brum</v>
       </c>
       <c r="C8" t="str">
         <v>Adulto</v>
@@ -759,7 +828,7 @@
         <v/>
       </c>
       <c r="E8">
-        <v>2580</v>
+        <v>4417</v>
       </c>
       <c r="F8" t="str">
         <v>Pendente</v>
@@ -773,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>João Paulo Silva</v>
+        <v>Maria Silva</v>
       </c>
       <c r="C9" t="str">
         <v>Adulto</v>
@@ -782,7 +851,7 @@
         <v/>
       </c>
       <c r="E9">
-        <v>4417</v>
+        <v>2550</v>
       </c>
       <c r="F9" t="str">
         <v>Pendente</v>
@@ -796,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Vanessa Brum</v>
+        <v>Ísis Silva</v>
       </c>
       <c r="C10" t="str">
         <v>Adulto</v>
@@ -805,7 +874,7 @@
         <v/>
       </c>
       <c r="E10">
-        <v>4417</v>
+        <v>6612</v>
       </c>
       <c r="F10" t="str">
         <v>Pendente</v>
@@ -819,7 +888,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Leonardo Brum</v>
+        <v>Graça Teresinha</v>
       </c>
       <c r="C11" t="str">
         <v>Adulto</v>
@@ -828,7 +897,7 @@
         <v/>
       </c>
       <c r="E11">
-        <v>4417</v>
+        <v>1754</v>
       </c>
       <c r="F11" t="str">
         <v>Pendente</v>
@@ -842,7 +911,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Maria Silva</v>
+        <v>Renato</v>
       </c>
       <c r="C12" t="str">
         <v>Adulto</v>
@@ -851,7 +920,7 @@
         <v/>
       </c>
       <c r="E12">
-        <v>2550</v>
+        <v>1754</v>
       </c>
       <c r="F12" t="str">
         <v>Pendente</v>
@@ -865,7 +934,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Ísis Silva</v>
+        <v>Cheila Machado</v>
       </c>
       <c r="C13" t="str">
         <v>Adulto</v>
@@ -874,7 +943,7 @@
         <v/>
       </c>
       <c r="E13">
-        <v>6612</v>
+        <v>5820</v>
       </c>
       <c r="F13" t="str">
         <v>Pendente</v>
@@ -888,7 +957,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Graça Silva</v>
+        <v>Paulo Machado</v>
       </c>
       <c r="C14" t="str">
         <v>Adulto</v>
@@ -897,7 +966,7 @@
         <v/>
       </c>
       <c r="E14">
-        <v>1754</v>
+        <v>5820</v>
       </c>
       <c r="F14" t="str">
         <v>Pendente</v>
@@ -911,7 +980,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Renato</v>
+        <v>Gustavo Machado</v>
       </c>
       <c r="C15" t="str">
         <v>Adulto</v>
@@ -920,7 +989,7 @@
         <v/>
       </c>
       <c r="E15">
-        <v>1754</v>
+        <v>5820</v>
       </c>
       <c r="F15" t="str">
         <v>Pendente</v>
@@ -934,7 +1003,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Cheila Machado</v>
+        <v>Yasmin Teixeira</v>
       </c>
       <c r="C16" t="str">
         <v>Adulto</v>
@@ -957,7 +1026,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Paulo Machado</v>
+        <v>Arthur Machado</v>
       </c>
       <c r="C17" t="str">
         <v>Adulto</v>
@@ -980,7 +1049,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Gustavo Machado</v>
+        <v>Rafaella Buttenbender</v>
       </c>
       <c r="C18" t="str">
         <v>Adulto</v>
@@ -989,7 +1058,7 @@
         <v/>
       </c>
       <c r="E18">
-        <v>8262</v>
+        <v>5820</v>
       </c>
       <c r="F18" t="str">
         <v>Pendente</v>
@@ -1003,7 +1072,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Yasmin Teixeira</v>
+        <v>Vilson</v>
       </c>
       <c r="C19" t="str">
         <v>Adulto</v>
@@ -1012,7 +1081,7 @@
         <v/>
       </c>
       <c r="E19">
-        <v>8262</v>
+        <v>7361</v>
       </c>
       <c r="F19" t="str">
         <v>Pendente</v>
@@ -1026,7 +1095,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Arthur Machado</v>
+        <v>Rita</v>
       </c>
       <c r="C20" t="str">
         <v>Adulto</v>
@@ -1035,7 +1104,7 @@
         <v/>
       </c>
       <c r="E20">
-        <v>4410</v>
+        <v>7361</v>
       </c>
       <c r="F20" t="str">
         <v>Pendente</v>
@@ -1049,7 +1118,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Rafaella Buttenbender</v>
+        <v>Rose</v>
       </c>
       <c r="C21" t="str">
         <v>Adulto</v>
@@ -1058,7 +1127,7 @@
         <v/>
       </c>
       <c r="E21">
-        <v>4410</v>
+        <v>1636</v>
       </c>
       <c r="F21" t="str">
         <v>Pendente</v>
@@ -1072,7 +1141,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Nice</v>
+        <v>Ronei</v>
       </c>
       <c r="C22" t="str">
         <v>Adulto</v>
@@ -1081,7 +1150,7 @@
         <v/>
       </c>
       <c r="E22">
-        <v>2309</v>
+        <v>1636</v>
       </c>
       <c r="F22" t="str">
         <v>Pendente</v>
@@ -1095,7 +1164,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Clemi</v>
+        <v>Volmar Machado</v>
       </c>
       <c r="C23" t="str">
         <v>Adulto</v>
@@ -1104,7 +1173,7 @@
         <v/>
       </c>
       <c r="E23">
-        <v>1111</v>
+        <v>8234</v>
       </c>
       <c r="F23" t="str">
         <v>Pendente</v>
@@ -1118,7 +1187,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Vilson</v>
+        <v>Lurdes</v>
       </c>
       <c r="C24" t="str">
         <v>Adulto</v>
@@ -1127,7 +1196,7 @@
         <v/>
       </c>
       <c r="E24">
-        <v>7361</v>
+        <v>2222</v>
       </c>
       <c r="F24" t="str">
         <v>Pendente</v>
@@ -1141,7 +1210,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Rita</v>
+        <v>Cecinha</v>
       </c>
       <c r="C25" t="str">
         <v>Adulto</v>
@@ -1150,7 +1219,7 @@
         <v/>
       </c>
       <c r="E25">
-        <v>7361</v>
+        <v>3333</v>
       </c>
       <c r="F25" t="str">
         <v>Pendente</v>
@@ -1164,7 +1233,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Rose</v>
+        <v>Claudete Freitas</v>
       </c>
       <c r="C26" t="str">
         <v>Adulto</v>
@@ -1173,7 +1242,7 @@
         <v/>
       </c>
       <c r="E26">
-        <v>1636</v>
+        <v>8990</v>
       </c>
       <c r="F26" t="str">
         <v>Pendente</v>
@@ -1187,7 +1256,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>Ronei</v>
+        <v>Elizabeth</v>
       </c>
       <c r="C27" t="str">
         <v>Adulto</v>
@@ -1196,7 +1265,7 @@
         <v/>
       </c>
       <c r="E27">
-        <v>1636</v>
+        <v>8990</v>
       </c>
       <c r="F27" t="str">
         <v>Pendente</v>
@@ -1210,7 +1279,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Volmar Machado</v>
+        <v>Lucas Garcia</v>
       </c>
       <c r="C28" t="str">
         <v>Adulto</v>
@@ -1219,7 +1288,7 @@
         <v/>
       </c>
       <c r="E28">
-        <v>8234</v>
+        <v>2558</v>
       </c>
       <c r="F28" t="str">
         <v>Pendente</v>
@@ -1233,7 +1302,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Lurdes</v>
+        <v>Monique</v>
       </c>
       <c r="C29" t="str">
         <v>Adulto</v>
@@ -1242,7 +1311,7 @@
         <v/>
       </c>
       <c r="E29">
-        <v>2222</v>
+        <v>2558</v>
       </c>
       <c r="F29" t="str">
         <v>Pendente</v>
@@ -1256,7 +1325,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Cecinha</v>
+        <v>Ivonete</v>
       </c>
       <c r="C30" t="str">
         <v>Adulto</v>
@@ -1265,7 +1334,7 @@
         <v/>
       </c>
       <c r="E30">
-        <v>3333</v>
+        <v>5555</v>
       </c>
       <c r="F30" t="str">
         <v>Pendente</v>
@@ -1279,7 +1348,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Claudete Freitas</v>
+        <v>Einar Marques</v>
       </c>
       <c r="C31" t="str">
         <v>Adulto</v>
@@ -1288,7 +1357,7 @@
         <v/>
       </c>
       <c r="E31">
-        <v>8990</v>
+        <v>5496</v>
       </c>
       <c r="F31" t="str">
         <v>Pendente</v>
@@ -1302,7 +1371,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>Elizabeth</v>
+        <v>Fabiana Gomes</v>
       </c>
       <c r="C32" t="str">
         <v>Adulto</v>
@@ -1311,7 +1380,7 @@
         <v/>
       </c>
       <c r="E32">
-        <v>8990</v>
+        <v>5496</v>
       </c>
       <c r="F32" t="str">
         <v>Pendente</v>
@@ -1325,7 +1394,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>Lucas Garcia</v>
+        <v>Marco Martins</v>
       </c>
       <c r="C33" t="str">
         <v>Adulto</v>
@@ -1334,7 +1403,7 @@
         <v/>
       </c>
       <c r="E33">
-        <v>2558</v>
+        <v>5001</v>
       </c>
       <c r="F33" t="str">
         <v>Pendente</v>
@@ -1348,7 +1417,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>Monique</v>
+        <v>Rose Tormann</v>
       </c>
       <c r="C34" t="str">
         <v>Adulto</v>
@@ -1357,7 +1426,7 @@
         <v/>
       </c>
       <c r="E34">
-        <v>2558</v>
+        <v>5001</v>
       </c>
       <c r="F34" t="str">
         <v>Pendente</v>
@@ -1371,7 +1440,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>Ivonete</v>
+        <v>Júlio</v>
       </c>
       <c r="C35" t="str">
         <v>Adulto</v>
@@ -1380,7 +1449,7 @@
         <v/>
       </c>
       <c r="E35">
-        <v>5555</v>
+        <v>5124</v>
       </c>
       <c r="F35" t="str">
         <v>Pendente</v>
@@ -1394,7 +1463,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>Einar Marques</v>
+        <v>Jocasta</v>
       </c>
       <c r="C36" t="str">
         <v>Adulto</v>
@@ -1403,7 +1472,7 @@
         <v/>
       </c>
       <c r="E36">
-        <v>5496</v>
+        <v>5124</v>
       </c>
       <c r="F36" t="str">
         <v>Pendente</v>
@@ -1417,7 +1486,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>Fabiana Gomes</v>
+        <v>Fábio</v>
       </c>
       <c r="C37" t="str">
         <v>Adulto</v>
@@ -1426,7 +1495,7 @@
         <v/>
       </c>
       <c r="E37">
-        <v>5496</v>
+        <v>9772</v>
       </c>
       <c r="F37" t="str">
         <v>Pendente</v>
@@ -1440,7 +1509,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>Marco Martins</v>
+        <v>Cleci</v>
       </c>
       <c r="C38" t="str">
         <v>Adulto</v>
@@ -1449,7 +1518,7 @@
         <v/>
       </c>
       <c r="E38">
-        <v>5001</v>
+        <v>9772</v>
       </c>
       <c r="F38" t="str">
         <v>Pendente</v>
@@ -1463,7 +1532,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>Rose Tormann</v>
+        <v>Yasmin</v>
       </c>
       <c r="C39" t="str">
         <v>Adulto</v>
@@ -1472,7 +1541,7 @@
         <v/>
       </c>
       <c r="E39">
-        <v>5001</v>
+        <v>9772</v>
       </c>
       <c r="F39" t="str">
         <v>Pendente</v>
@@ -1486,7 +1555,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>Júlio</v>
+        <v>Paulete</v>
       </c>
       <c r="C40" t="str">
         <v>Adulto</v>
@@ -1495,7 +1564,7 @@
         <v/>
       </c>
       <c r="E40">
-        <v>5124</v>
+        <v>2978</v>
       </c>
       <c r="F40" t="str">
         <v>Pendente</v>
@@ -1509,7 +1578,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>Jocasta</v>
+        <v>Isaura Monteiro</v>
       </c>
       <c r="C41" t="str">
         <v>Adulto</v>
@@ -1518,7 +1587,7 @@
         <v/>
       </c>
       <c r="E41">
-        <v>5124</v>
+        <v>4666</v>
       </c>
       <c r="F41" t="str">
         <v>Pendente</v>
@@ -1532,7 +1601,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>Fábio</v>
+        <v>Vanessa Kissler</v>
       </c>
       <c r="C42" t="str">
         <v>Adulto</v>
@@ -1541,7 +1610,7 @@
         <v/>
       </c>
       <c r="E42">
-        <v>9772</v>
+        <v>1228</v>
       </c>
       <c r="F42" t="str">
         <v>Pendente</v>
@@ -1555,7 +1624,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>Cleci</v>
+        <v>Guilherme Becker</v>
       </c>
       <c r="C43" t="str">
         <v>Adulto</v>
@@ -1564,7 +1633,7 @@
         <v/>
       </c>
       <c r="E43">
-        <v>9772</v>
+        <v>1228</v>
       </c>
       <c r="F43" t="str">
         <v>Pendente</v>
@@ -1578,7 +1647,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>Yasmin</v>
+        <v>Maria Eduarda Rocha</v>
       </c>
       <c r="C44" t="str">
         <v>Adulto</v>
@@ -1587,7 +1656,7 @@
         <v/>
       </c>
       <c r="E44">
-        <v>9772</v>
+        <v>5690</v>
       </c>
       <c r="F44" t="str">
         <v>Pendente</v>
@@ -1601,7 +1670,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>Paulete</v>
+        <v>Ivan</v>
       </c>
       <c r="C45" t="str">
         <v>Adulto</v>
@@ -1610,7 +1679,7 @@
         <v/>
       </c>
       <c r="E45">
-        <v>2978</v>
+        <v>5690</v>
       </c>
       <c r="F45" t="str">
         <v>Pendente</v>
@@ -1624,7 +1693,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>Isaura Monteiro</v>
+        <v>Ivan Pedro Freitas</v>
       </c>
       <c r="C46" t="str">
         <v>Adulto</v>
@@ -1633,13 +1702,13 @@
         <v/>
       </c>
       <c r="E46">
-        <v>4666</v>
+        <v>1001</v>
       </c>
       <c r="F46" t="str">
         <v>Pendente</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>29/04/2025</v>
       </c>
     </row>
     <row r="47">
@@ -1647,7 +1716,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>Vanessa Kissler</v>
+        <v>Erick Almeida</v>
       </c>
       <c r="C47" t="str">
         <v>Adulto</v>
@@ -1656,7 +1725,7 @@
         <v/>
       </c>
       <c r="E47">
-        <v>1228</v>
+        <v>9251</v>
       </c>
       <c r="F47" t="str">
         <v>Pendente</v>
@@ -1670,7 +1739,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Guilherme Becker</v>
+        <v>Matheus</v>
       </c>
       <c r="C48" t="str">
         <v>Adulto</v>
@@ -1679,7 +1748,7 @@
         <v/>
       </c>
       <c r="E48">
-        <v>1228</v>
+        <v>9251</v>
       </c>
       <c r="F48" t="str">
         <v>Pendente</v>
@@ -1693,7 +1762,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>Maria Eduarda Rocha</v>
+        <v>Guilherme Mocelin</v>
       </c>
       <c r="C49" t="str">
         <v>Adulto</v>
@@ -1702,13 +1771,13 @@
         <v/>
       </c>
       <c r="E49">
-        <v>5690</v>
+        <v>9871</v>
       </c>
       <c r="F49" t="str">
         <v>Pendente</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>20/04/2025</v>
       </c>
     </row>
     <row r="50">
@@ -1716,7 +1785,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>Ivan</v>
+        <v>Caroline Farias</v>
       </c>
       <c r="C50" t="str">
         <v>Adulto</v>
@@ -1725,7 +1794,7 @@
         <v/>
       </c>
       <c r="E50">
-        <v>5690</v>
+        <v>8228</v>
       </c>
       <c r="F50" t="str">
         <v>Pendente</v>
@@ -1739,7 +1808,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Ivan Pedro Freitas</v>
+        <v>Marcelo Vergara</v>
       </c>
       <c r="C51" t="str">
         <v>Adulto</v>
@@ -1748,7 +1817,7 @@
         <v/>
       </c>
       <c r="E51">
-        <v>1001</v>
+        <v>8228</v>
       </c>
       <c r="F51" t="str">
         <v>Pendente</v>
@@ -1762,7 +1831,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>Erick Almeida</v>
+        <v>Mateus Leote</v>
       </c>
       <c r="C52" t="str">
         <v>Adulto</v>
@@ -1771,7 +1840,7 @@
         <v/>
       </c>
       <c r="E52">
-        <v>9251</v>
+        <v>5990</v>
       </c>
       <c r="F52" t="str">
         <v>Pendente</v>
@@ -1785,7 +1854,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>Matheus</v>
+        <v>Julia Cardoso</v>
       </c>
       <c r="C53" t="str">
         <v>Adulto</v>
@@ -1794,7 +1863,7 @@
         <v/>
       </c>
       <c r="E53">
-        <v>9251</v>
+        <v>5990</v>
       </c>
       <c r="F53" t="str">
         <v>Pendente</v>
@@ -1808,7 +1877,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>Guilherme Mocelin</v>
+        <v>Sara Rubia</v>
       </c>
       <c r="C54" t="str">
         <v>Adulto</v>
@@ -1817,7 +1886,7 @@
         <v/>
       </c>
       <c r="E54">
-        <v>9871</v>
+        <v>8326</v>
       </c>
       <c r="F54" t="str">
         <v>Pendente</v>
@@ -1831,7 +1900,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>Caroline Farias</v>
+        <v>Eduarda Leal</v>
       </c>
       <c r="C55" t="str">
         <v>Adulto</v>
@@ -1840,7 +1909,7 @@
         <v/>
       </c>
       <c r="E55">
-        <v>8228</v>
+        <v>3277</v>
       </c>
       <c r="F55" t="str">
         <v>Pendente</v>
@@ -1854,7 +1923,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>Marcelo Vergara</v>
+        <v>Gabriela</v>
       </c>
       <c r="C56" t="str">
         <v>Adulto</v>
@@ -1863,7 +1932,7 @@
         <v/>
       </c>
       <c r="E56">
-        <v>8228</v>
+        <v>7792</v>
       </c>
       <c r="F56" t="str">
         <v>Pendente</v>
@@ -1877,7 +1946,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>Mateus Leote</v>
+        <v>Eduardo Viegas</v>
       </c>
       <c r="C57" t="str">
         <v>Adulto</v>
@@ -1886,7 +1955,7 @@
         <v/>
       </c>
       <c r="E57">
-        <v>5990</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="str">
         <v>Pendente</v>
@@ -1900,7 +1969,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>Julia Cardoso</v>
+        <v>Gabriele Knop</v>
       </c>
       <c r="C58" t="str">
         <v>Adulto</v>
@@ -1909,7 +1978,7 @@
         <v/>
       </c>
       <c r="E58">
-        <v>5990</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="str">
         <v>Pendente</v>
@@ -1923,7 +1992,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>Sara Rubia</v>
+        <v>Eduardo Kern</v>
       </c>
       <c r="C59" t="str">
         <v>Adulto</v>
@@ -1932,7 +2001,7 @@
         <v/>
       </c>
       <c r="E59">
-        <v>8326</v>
+        <v>8504</v>
       </c>
       <c r="F59" t="str">
         <v>Pendente</v>
@@ -1946,7 +2015,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>Eduarda Leal</v>
+        <v>Henrique Demarchi</v>
       </c>
       <c r="C60" t="str">
         <v>Adulto</v>
@@ -1955,13 +2024,13 @@
         <v/>
       </c>
       <c r="E60">
-        <v>3277</v>
+        <v>2036</v>
       </c>
       <c r="F60" t="str">
         <v>Pendente</v>
       </c>
       <c r="G60" t="str">
-        <v/>
+        <v>04/05/2025</v>
       </c>
     </row>
     <row r="61">
@@ -1969,7 +2038,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Gabriela</v>
+        <v>Franciele de Leon</v>
       </c>
       <c r="C61" t="str">
         <v>Adulto</v>
@@ -1978,7 +2047,7 @@
         <v/>
       </c>
       <c r="E61">
-        <v>7792</v>
+        <v>8778</v>
       </c>
       <c r="F61" t="str">
         <v>Pendente</v>
@@ -1992,7 +2061,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Eduardo Viegas</v>
+        <v>Bruno Erling</v>
       </c>
       <c r="C62" t="str">
         <v>Adulto</v>
@@ -2001,7 +2070,7 @@
         <v/>
       </c>
       <c r="E62">
-        <v>5447</v>
+        <v>8778</v>
       </c>
       <c r="F62" t="str">
         <v>Pendente</v>
@@ -2015,7 +2084,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Gabriele Knop</v>
+        <v>Sandriele de Leon</v>
       </c>
       <c r="C63" t="str">
         <v>Adulto</v>
@@ -2024,7 +2093,7 @@
         <v/>
       </c>
       <c r="E63">
-        <v>5447</v>
+        <v>4142</v>
       </c>
       <c r="F63" t="str">
         <v>Pendente</v>
@@ -2038,7 +2107,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>Eduardo Kern</v>
+        <v>Giuvanni Bagatini</v>
       </c>
       <c r="C64" t="str">
         <v>Adulto</v>
@@ -2047,7 +2116,7 @@
         <v/>
       </c>
       <c r="E64">
-        <v>8504</v>
+        <v>4142</v>
       </c>
       <c r="F64" t="str">
         <v>Pendente</v>
@@ -2061,7 +2130,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Henrique Demarchi</v>
+        <v>Rochele de Leon</v>
       </c>
       <c r="C65" t="str">
         <v>Adulto</v>
@@ -2070,13 +2139,13 @@
         <v/>
       </c>
       <c r="E65">
-        <v>2036</v>
+        <v>3163</v>
       </c>
       <c r="F65" t="str">
         <v>Pendente</v>
       </c>
       <c r="G65" t="str">
-        <v>19/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -2084,7 +2153,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Franciele de Leon</v>
+        <v>Sandro Marques</v>
       </c>
       <c r="C66" t="str">
         <v>Adulto</v>
@@ -2093,7 +2162,7 @@
         <v/>
       </c>
       <c r="E66">
-        <v>8778</v>
+        <v>3163</v>
       </c>
       <c r="F66" t="str">
         <v>Pendente</v>
@@ -2107,7 +2176,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>Bruno Erling</v>
+        <v>Cleusa</v>
       </c>
       <c r="C67" t="str">
         <v>Adulto</v>
@@ -2116,7 +2185,7 @@
         <v/>
       </c>
       <c r="E67">
-        <v>8778</v>
+        <v>6684</v>
       </c>
       <c r="F67" t="str">
         <v>Pendente</v>
@@ -2130,7 +2199,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>Sandriele de Leon</v>
+        <v>Luiz Airton</v>
       </c>
       <c r="C68" t="str">
         <v>Adulto</v>
@@ -2139,7 +2208,7 @@
         <v/>
       </c>
       <c r="E68">
-        <v>4142</v>
+        <v>6684</v>
       </c>
       <c r="F68" t="str">
         <v>Pendente</v>
@@ -2153,7 +2222,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>Giuvanni Bagatini</v>
+        <v>Angela</v>
       </c>
       <c r="C69" t="str">
         <v>Adulto</v>
@@ -2162,7 +2231,7 @@
         <v/>
       </c>
       <c r="E69">
-        <v>4142</v>
+        <v>9860</v>
       </c>
       <c r="F69" t="str">
         <v>Pendente</v>
@@ -2176,7 +2245,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>Rochele de Leon</v>
+        <v>Alexandre</v>
       </c>
       <c r="C70" t="str">
         <v>Adulto</v>
@@ -2185,7 +2254,7 @@
         <v/>
       </c>
       <c r="E70">
-        <v>3163</v>
+        <v>9860</v>
       </c>
       <c r="F70" t="str">
         <v>Pendente</v>
@@ -2199,7 +2268,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>Sandro Marques</v>
+        <v>Amanda</v>
       </c>
       <c r="C71" t="str">
         <v>Adulto</v>
@@ -2208,13 +2277,13 @@
         <v/>
       </c>
       <c r="E71">
-        <v>3163</v>
+        <v>1558</v>
       </c>
       <c r="F71" t="str">
         <v>Pendente</v>
       </c>
       <c r="G71" t="str">
-        <v/>
+        <v>19/04/2025</v>
       </c>
     </row>
     <row r="72">
@@ -2222,7 +2291,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>Cleusa</v>
+        <v>Giuliano</v>
       </c>
       <c r="C72" t="str">
         <v>Adulto</v>
@@ -2231,13 +2300,13 @@
         <v/>
       </c>
       <c r="E72">
-        <v>6684</v>
+        <v>1558</v>
       </c>
       <c r="F72" t="str">
         <v>Pendente</v>
       </c>
       <c r="G72" t="str">
-        <v/>
+        <v>19/04/2025</v>
       </c>
     </row>
     <row r="73">
@@ -2245,7 +2314,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>Luiz Airton</v>
+        <v>Natalia</v>
       </c>
       <c r="C73" t="str">
         <v>Adulto</v>
@@ -2254,7 +2323,7 @@
         <v/>
       </c>
       <c r="E73">
-        <v>6684</v>
+        <v>8602</v>
       </c>
       <c r="F73" t="str">
         <v>Pendente</v>
@@ -2268,7 +2337,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>Angela</v>
+        <v>Guilherme Lobo</v>
       </c>
       <c r="C74" t="str">
         <v>Adulto</v>
@@ -2291,16 +2360,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>Alexandre</v>
+        <v>Daniel</v>
       </c>
       <c r="C75" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D75" t="str">
         <v/>
       </c>
       <c r="E75">
-        <v>8602</v>
+        <v>5124</v>
       </c>
       <c r="F75" t="str">
         <v>Pendente</v>
@@ -2314,22 +2383,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>Amanda</v>
+        <v>Lorenzo</v>
       </c>
       <c r="C76" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D76" t="str">
         <v/>
       </c>
       <c r="E76">
-        <v>1558</v>
+        <v>4142</v>
       </c>
       <c r="F76" t="str">
         <v>Pendente</v>
       </c>
       <c r="G76" t="str">
-        <v>19/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -2337,22 +2406,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>Giuliano</v>
+        <v>Julia</v>
       </c>
       <c r="C77" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D77" t="str">
         <v/>
       </c>
       <c r="E77">
-        <v>1558</v>
+        <v>5124</v>
       </c>
       <c r="F77" t="str">
         <v>Pendente</v>
       </c>
       <c r="G77" t="str">
-        <v>19/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -2360,16 +2429,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>Natalia</v>
+        <v>Julia Erling</v>
       </c>
       <c r="C78" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D78" t="str">
         <v/>
       </c>
       <c r="E78">
-        <v>8602</v>
+        <v>8778</v>
       </c>
       <c r="F78" t="str">
         <v>Pendente</v>
@@ -2383,10 +2452,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>Guilherme Lobo</v>
+        <v>Theo</v>
       </c>
       <c r="C79" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D79" t="str">
         <v/>
@@ -2406,16 +2475,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>Ana Paula Rangel</v>
+        <v>Luisa Silva</v>
       </c>
       <c r="C80" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D80" t="str">
         <v/>
       </c>
       <c r="E80">
-        <v>9922</v>
+        <v>4417</v>
       </c>
       <c r="F80" t="str">
         <v>Pendente</v>
@@ -2429,22 +2498,22 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>Cesar Maia</v>
+        <v>Antonio</v>
       </c>
       <c r="C81" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D81" t="str">
         <v/>
       </c>
       <c r="E81">
-        <v>9922</v>
+        <v>1558</v>
       </c>
       <c r="F81" t="str">
         <v>Pendente</v>
       </c>
       <c r="G81" t="str">
-        <v/>
+        <v>19/04/2025</v>
       </c>
     </row>
     <row r="82">
@@ -2452,16 +2521,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>Daniel</v>
+        <v>Rafael Dutra</v>
       </c>
       <c r="C82" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D82" t="str">
         <v/>
       </c>
       <c r="E82">
-        <v>5124</v>
+        <v>7947</v>
       </c>
       <c r="F82" t="str">
         <v>Pendente</v>
@@ -2475,16 +2544,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>Lorenzo</v>
+        <v>Hérica Marques</v>
       </c>
       <c r="C83" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D83" t="str">
         <v/>
       </c>
       <c r="E83">
-        <v>4142</v>
+        <v>8284</v>
       </c>
       <c r="F83" t="str">
         <v>Pendente</v>
@@ -2498,16 +2567,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>Julia</v>
+        <v>Thomas</v>
       </c>
       <c r="C84" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D84" t="str">
         <v/>
       </c>
       <c r="E84">
-        <v>5124</v>
+        <v>8284</v>
       </c>
       <c r="F84" t="str">
         <v>Pendente</v>
@@ -2521,7 +2590,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>Julia Erling</v>
+        <v>Gustavo</v>
       </c>
       <c r="C85" t="str">
         <v>CRIANCA</v>
@@ -2530,7 +2599,7 @@
         <v/>
       </c>
       <c r="E85">
-        <v>8778</v>
+        <v>8284</v>
       </c>
       <c r="F85" t="str">
         <v>Pendente</v>
@@ -2544,22 +2613,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>Antonio</v>
+        <v>Guilherme</v>
       </c>
       <c r="C86" t="str">
-        <v>CRIANCA (5 anos)</v>
-      </c>
-      <c r="D86">
-        <v>5</v>
+        <v>CRIANCA</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
       </c>
       <c r="E86">
-        <v>1558</v>
+        <v>8284</v>
       </c>
       <c r="F86" t="str">
         <v>Pendente</v>
       </c>
       <c r="G86" t="str">
-        <v>19/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -2567,7 +2636,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>Theo</v>
+        <v>Sofia</v>
       </c>
       <c r="C87" t="str">
         <v>CRIANCA</v>
@@ -2576,7 +2645,7 @@
         <v/>
       </c>
       <c r="E87">
-        <v>8602</v>
+        <v>8284</v>
       </c>
       <c r="F87" t="str">
         <v>Pendente</v>
@@ -2590,22 +2659,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>Luisa Silva</v>
+        <v>João Pedro Marçal</v>
       </c>
       <c r="C88" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D88" t="str">
         <v/>
       </c>
       <c r="E88">
-        <v>4417</v>
+        <v>2036</v>
       </c>
       <c r="F88" t="str">
         <v>Pendente</v>
       </c>
       <c r="G88" t="str">
-        <v/>
+        <v>04/05/2025</v>
       </c>
     </row>
   </sheetData>
@@ -2644,7 +2713,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2653,16 +2722,16 @@
         <v>87</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/graduation-api/convidados_confirmados.xlsx
+++ b/graduation-api/convidados_confirmados.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>Confirmado</v>
       </c>
       <c r="G2" t="str">
-        <v>14/05/2025</v>
+        <v>15/05/2025</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         <v>Confirmado</v>
       </c>
       <c r="G3" t="str">
-        <v>14/05/2025</v>
+        <v>15/05/2025</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>Confirmado</v>
       </c>
       <c r="G4" t="str">
-        <v>14/05/2025</v>
+        <v>15/05/2025</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>João Batista</v>
+        <v>Sandra Silva</v>
       </c>
       <c r="C7" t="str">
         <v>Adulto</v>
@@ -554,13 +554,13 @@
         <v/>
       </c>
       <c r="E7">
-        <v>3261</v>
+        <v>6744</v>
       </c>
       <c r="F7" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G7" t="str">
-        <v>13/05/2025</v>
+        <v>14/05/2025</v>
       </c>
     </row>
     <row r="8">
@@ -568,7 +568,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Benjamin Silva</v>
+        <v>Antônio Renê Silva</v>
       </c>
       <c r="C8" t="str">
         <v>Adulto</v>
@@ -577,13 +577,13 @@
         <v/>
       </c>
       <c r="E8">
-        <v>3261</v>
+        <v>6744</v>
       </c>
       <c r="F8" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G8" t="str">
-        <v>13/05/2025</v>
+        <v>14/05/2025</v>
       </c>
     </row>
     <row r="9">
@@ -591,22 +591,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Benicio Silva</v>
+        <v>Nicole Silva</v>
       </c>
       <c r="C9" t="str">
-        <v>CRIANCA (10 anos)</v>
-      </c>
-      <c r="D9">
-        <v>10</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
       </c>
       <c r="E9">
-        <v>3261</v>
+        <v>2580</v>
       </c>
       <c r="F9" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G9" t="str">
-        <v>13/05/2025</v>
+        <v>14/05/2025</v>
       </c>
     </row>
     <row r="10">
@@ -614,27 +614,280 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Joaquim Silva</v>
+        <v>Pedro Tremarin</v>
       </c>
       <c r="C10" t="str">
-        <v>CRIANCA (8 anos)</v>
-      </c>
-      <c r="D10">
-        <v>8</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
       </c>
       <c r="E10">
-        <v>3261</v>
+        <v>2580</v>
       </c>
       <c r="F10" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G10" t="str">
+        <v>14/05/2025</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>João Paulo Silva</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11">
+        <v>4417</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G11" t="str">
+        <v>14/05/2025</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Vanessa Brum</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>4417</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G12" t="str">
+        <v>14/05/2025</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Leonardo Brum</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13">
+        <v>4417</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G13" t="str">
+        <v>14/05/2025</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Maria Silva</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14">
+        <v>2550</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G14" t="str">
+        <v>14/05/2025</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>João Batista</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15">
+        <v>3261</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G15" t="str">
         <v>13/05/2025</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Guilherme Mocelin</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16">
+        <v>9871</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G16" t="str">
+        <v>14/05/2025</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Luisa Silva</v>
+      </c>
+      <c r="C17" t="str">
+        <v>CRIANCA (7 anos)</v>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>4417</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G17" t="str">
+        <v>14/05/2025</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Benjamin Silva</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18">
+        <v>3261</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G18" t="str">
+        <v>13/05/2025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Benicio Silva</v>
+      </c>
+      <c r="C19" t="str">
+        <v>CRIANCA (10 anos)</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19">
+        <v>3261</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G19" t="str">
+        <v>13/05/2025</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Joaquim Silva</v>
+      </c>
+      <c r="C20" t="str">
+        <v>CRIANCA (8 anos)</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>3261</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G20" t="str">
+        <v>13/05/2025</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Teste</v>
+      </c>
+      <c r="C21" t="str">
+        <v>CRIANCA (2 anos)</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>1240</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Confirmado</v>
+      </c>
+      <c r="G21" t="str">
+        <v>15/05/2025</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -651,7 +904,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G78"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -681,7 +934,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Sandra Silva</v>
+        <v>Ísis Silva</v>
       </c>
       <c r="C2" t="str">
         <v>Adulto</v>
@@ -690,7 +943,7 @@
         <v/>
       </c>
       <c r="E2">
-        <v>6744</v>
+        <v>6612</v>
       </c>
       <c r="F2" t="str">
         <v>Pendente</v>
@@ -704,7 +957,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Antônio Renê Silva</v>
+        <v>Graça Teresinha</v>
       </c>
       <c r="C3" t="str">
         <v>Adulto</v>
@@ -713,7 +966,7 @@
         <v/>
       </c>
       <c r="E3">
-        <v>6744</v>
+        <v>1754</v>
       </c>
       <c r="F3" t="str">
         <v>Pendente</v>
@@ -727,7 +980,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Nicole Silva</v>
+        <v>Renato</v>
       </c>
       <c r="C4" t="str">
         <v>Adulto</v>
@@ -736,7 +989,7 @@
         <v/>
       </c>
       <c r="E4">
-        <v>2580</v>
+        <v>1754</v>
       </c>
       <c r="F4" t="str">
         <v>Pendente</v>
@@ -750,7 +1003,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Pedro Tremarin</v>
+        <v>Cheila Machado</v>
       </c>
       <c r="C5" t="str">
         <v>Adulto</v>
@@ -759,7 +1012,7 @@
         <v/>
       </c>
       <c r="E5">
-        <v>2580</v>
+        <v>5820</v>
       </c>
       <c r="F5" t="str">
         <v>Pendente</v>
@@ -773,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>João Paulo Silva</v>
+        <v>Paulo Machado</v>
       </c>
       <c r="C6" t="str">
         <v>Adulto</v>
@@ -782,7 +1035,7 @@
         <v/>
       </c>
       <c r="E6">
-        <v>4417</v>
+        <v>5820</v>
       </c>
       <c r="F6" t="str">
         <v>Pendente</v>
@@ -796,7 +1049,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Vanessa Brum</v>
+        <v>Gustavo Machado</v>
       </c>
       <c r="C7" t="str">
         <v>Adulto</v>
@@ -805,7 +1058,7 @@
         <v/>
       </c>
       <c r="E7">
-        <v>4417</v>
+        <v>5820</v>
       </c>
       <c r="F7" t="str">
         <v>Pendente</v>
@@ -819,7 +1072,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Leonardo Brum</v>
+        <v>Yasmin Teixeira</v>
       </c>
       <c r="C8" t="str">
         <v>Adulto</v>
@@ -828,7 +1081,7 @@
         <v/>
       </c>
       <c r="E8">
-        <v>4417</v>
+        <v>5820</v>
       </c>
       <c r="F8" t="str">
         <v>Pendente</v>
@@ -842,7 +1095,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Maria Silva</v>
+        <v>Arthur Machado</v>
       </c>
       <c r="C9" t="str">
         <v>Adulto</v>
@@ -851,7 +1104,7 @@
         <v/>
       </c>
       <c r="E9">
-        <v>2550</v>
+        <v>5820</v>
       </c>
       <c r="F9" t="str">
         <v>Pendente</v>
@@ -865,7 +1118,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Ísis Silva</v>
+        <v>Rafaella Buttenbender</v>
       </c>
       <c r="C10" t="str">
         <v>Adulto</v>
@@ -874,7 +1127,7 @@
         <v/>
       </c>
       <c r="E10">
-        <v>6612</v>
+        <v>5820</v>
       </c>
       <c r="F10" t="str">
         <v>Pendente</v>
@@ -888,7 +1141,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Graça Teresinha</v>
+        <v>Vilson</v>
       </c>
       <c r="C11" t="str">
         <v>Adulto</v>
@@ -897,7 +1150,7 @@
         <v/>
       </c>
       <c r="E11">
-        <v>1754</v>
+        <v>7361</v>
       </c>
       <c r="F11" t="str">
         <v>Pendente</v>
@@ -911,7 +1164,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Renato</v>
+        <v>Rita</v>
       </c>
       <c r="C12" t="str">
         <v>Adulto</v>
@@ -920,7 +1173,7 @@
         <v/>
       </c>
       <c r="E12">
-        <v>1754</v>
+        <v>7361</v>
       </c>
       <c r="F12" t="str">
         <v>Pendente</v>
@@ -934,7 +1187,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Cheila Machado</v>
+        <v>Rose</v>
       </c>
       <c r="C13" t="str">
         <v>Adulto</v>
@@ -943,7 +1196,7 @@
         <v/>
       </c>
       <c r="E13">
-        <v>5820</v>
+        <v>1636</v>
       </c>
       <c r="F13" t="str">
         <v>Pendente</v>
@@ -957,7 +1210,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Paulo Machado</v>
+        <v>Ronei</v>
       </c>
       <c r="C14" t="str">
         <v>Adulto</v>
@@ -966,7 +1219,7 @@
         <v/>
       </c>
       <c r="E14">
-        <v>5820</v>
+        <v>1636</v>
       </c>
       <c r="F14" t="str">
         <v>Pendente</v>
@@ -980,7 +1233,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Gustavo Machado</v>
+        <v>Volmar Machado</v>
       </c>
       <c r="C15" t="str">
         <v>Adulto</v>
@@ -989,7 +1242,7 @@
         <v/>
       </c>
       <c r="E15">
-        <v>5820</v>
+        <v>8234</v>
       </c>
       <c r="F15" t="str">
         <v>Pendente</v>
@@ -1003,7 +1256,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Yasmin Teixeira</v>
+        <v>Lurdes</v>
       </c>
       <c r="C16" t="str">
         <v>Adulto</v>
@@ -1012,7 +1265,7 @@
         <v/>
       </c>
       <c r="E16">
-        <v>5820</v>
+        <v>2222</v>
       </c>
       <c r="F16" t="str">
         <v>Pendente</v>
@@ -1026,7 +1279,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Arthur Machado</v>
+        <v>Cecinha</v>
       </c>
       <c r="C17" t="str">
         <v>Adulto</v>
@@ -1035,7 +1288,7 @@
         <v/>
       </c>
       <c r="E17">
-        <v>5820</v>
+        <v>3333</v>
       </c>
       <c r="F17" t="str">
         <v>Pendente</v>
@@ -1049,7 +1302,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Rafaella Buttenbender</v>
+        <v>Claudete Freitas</v>
       </c>
       <c r="C18" t="str">
         <v>Adulto</v>
@@ -1058,7 +1311,7 @@
         <v/>
       </c>
       <c r="E18">
-        <v>5820</v>
+        <v>8990</v>
       </c>
       <c r="F18" t="str">
         <v>Pendente</v>
@@ -1072,7 +1325,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Vilson</v>
+        <v>Elizabeth</v>
       </c>
       <c r="C19" t="str">
         <v>Adulto</v>
@@ -1081,7 +1334,7 @@
         <v/>
       </c>
       <c r="E19">
-        <v>7361</v>
+        <v>8990</v>
       </c>
       <c r="F19" t="str">
         <v>Pendente</v>
@@ -1095,7 +1348,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Rita</v>
+        <v>Lucas Garcia</v>
       </c>
       <c r="C20" t="str">
         <v>Adulto</v>
@@ -1104,7 +1357,7 @@
         <v/>
       </c>
       <c r="E20">
-        <v>7361</v>
+        <v>2558</v>
       </c>
       <c r="F20" t="str">
         <v>Pendente</v>
@@ -1118,7 +1371,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Rose</v>
+        <v>Monique</v>
       </c>
       <c r="C21" t="str">
         <v>Adulto</v>
@@ -1127,7 +1380,7 @@
         <v/>
       </c>
       <c r="E21">
-        <v>1636</v>
+        <v>2558</v>
       </c>
       <c r="F21" t="str">
         <v>Pendente</v>
@@ -1141,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Ronei</v>
+        <v>Ivonete</v>
       </c>
       <c r="C22" t="str">
         <v>Adulto</v>
@@ -1150,7 +1403,7 @@
         <v/>
       </c>
       <c r="E22">
-        <v>1636</v>
+        <v>5555</v>
       </c>
       <c r="F22" t="str">
         <v>Pendente</v>
@@ -1164,7 +1417,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Volmar Machado</v>
+        <v>Einar Marques</v>
       </c>
       <c r="C23" t="str">
         <v>Adulto</v>
@@ -1173,7 +1426,7 @@
         <v/>
       </c>
       <c r="E23">
-        <v>8234</v>
+        <v>5496</v>
       </c>
       <c r="F23" t="str">
         <v>Pendente</v>
@@ -1187,7 +1440,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Lurdes</v>
+        <v>Fabiana Gomes</v>
       </c>
       <c r="C24" t="str">
         <v>Adulto</v>
@@ -1196,7 +1449,7 @@
         <v/>
       </c>
       <c r="E24">
-        <v>2222</v>
+        <v>5496</v>
       </c>
       <c r="F24" t="str">
         <v>Pendente</v>
@@ -1210,7 +1463,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Cecinha</v>
+        <v>Marco Martins</v>
       </c>
       <c r="C25" t="str">
         <v>Adulto</v>
@@ -1219,7 +1472,7 @@
         <v/>
       </c>
       <c r="E25">
-        <v>3333</v>
+        <v>5001</v>
       </c>
       <c r="F25" t="str">
         <v>Pendente</v>
@@ -1233,7 +1486,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Claudete Freitas</v>
+        <v>Rose Tormann</v>
       </c>
       <c r="C26" t="str">
         <v>Adulto</v>
@@ -1242,7 +1495,7 @@
         <v/>
       </c>
       <c r="E26">
-        <v>8990</v>
+        <v>5001</v>
       </c>
       <c r="F26" t="str">
         <v>Pendente</v>
@@ -1256,7 +1509,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>Elizabeth</v>
+        <v>Júlio</v>
       </c>
       <c r="C27" t="str">
         <v>Adulto</v>
@@ -1265,7 +1518,7 @@
         <v/>
       </c>
       <c r="E27">
-        <v>8990</v>
+        <v>5124</v>
       </c>
       <c r="F27" t="str">
         <v>Pendente</v>
@@ -1279,7 +1532,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Lucas Garcia</v>
+        <v>Jocasta</v>
       </c>
       <c r="C28" t="str">
         <v>Adulto</v>
@@ -1288,7 +1541,7 @@
         <v/>
       </c>
       <c r="E28">
-        <v>2558</v>
+        <v>5124</v>
       </c>
       <c r="F28" t="str">
         <v>Pendente</v>
@@ -1302,7 +1555,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Monique</v>
+        <v>Fábio</v>
       </c>
       <c r="C29" t="str">
         <v>Adulto</v>
@@ -1311,7 +1564,7 @@
         <v/>
       </c>
       <c r="E29">
-        <v>2558</v>
+        <v>9772</v>
       </c>
       <c r="F29" t="str">
         <v>Pendente</v>
@@ -1325,7 +1578,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Ivonete</v>
+        <v>Cleci</v>
       </c>
       <c r="C30" t="str">
         <v>Adulto</v>
@@ -1334,7 +1587,7 @@
         <v/>
       </c>
       <c r="E30">
-        <v>5555</v>
+        <v>9772</v>
       </c>
       <c r="F30" t="str">
         <v>Pendente</v>
@@ -1348,7 +1601,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Einar Marques</v>
+        <v>Yasmin</v>
       </c>
       <c r="C31" t="str">
         <v>Adulto</v>
@@ -1357,7 +1610,7 @@
         <v/>
       </c>
       <c r="E31">
-        <v>5496</v>
+        <v>9772</v>
       </c>
       <c r="F31" t="str">
         <v>Pendente</v>
@@ -1371,7 +1624,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>Fabiana Gomes</v>
+        <v>Paulete</v>
       </c>
       <c r="C32" t="str">
         <v>Adulto</v>
@@ -1380,7 +1633,7 @@
         <v/>
       </c>
       <c r="E32">
-        <v>5496</v>
+        <v>2978</v>
       </c>
       <c r="F32" t="str">
         <v>Pendente</v>
@@ -1394,7 +1647,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>Marco Martins</v>
+        <v>Isaura Monteiro</v>
       </c>
       <c r="C33" t="str">
         <v>Adulto</v>
@@ -1403,7 +1656,7 @@
         <v/>
       </c>
       <c r="E33">
-        <v>5001</v>
+        <v>4666</v>
       </c>
       <c r="F33" t="str">
         <v>Pendente</v>
@@ -1417,7 +1670,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>Rose Tormann</v>
+        <v>Vanessa Kissler</v>
       </c>
       <c r="C34" t="str">
         <v>Adulto</v>
@@ -1426,7 +1679,7 @@
         <v/>
       </c>
       <c r="E34">
-        <v>5001</v>
+        <v>1228</v>
       </c>
       <c r="F34" t="str">
         <v>Pendente</v>
@@ -1440,7 +1693,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>Júlio</v>
+        <v>Guilherme Becker</v>
       </c>
       <c r="C35" t="str">
         <v>Adulto</v>
@@ -1449,7 +1702,7 @@
         <v/>
       </c>
       <c r="E35">
-        <v>5124</v>
+        <v>1228</v>
       </c>
       <c r="F35" t="str">
         <v>Pendente</v>
@@ -1463,7 +1716,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>Jocasta</v>
+        <v>Maria Eduarda Rocha</v>
       </c>
       <c r="C36" t="str">
         <v>Adulto</v>
@@ -1472,7 +1725,7 @@
         <v/>
       </c>
       <c r="E36">
-        <v>5124</v>
+        <v>5690</v>
       </c>
       <c r="F36" t="str">
         <v>Pendente</v>
@@ -1486,7 +1739,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>Fábio</v>
+        <v>Ivan</v>
       </c>
       <c r="C37" t="str">
         <v>Adulto</v>
@@ -1495,7 +1748,7 @@
         <v/>
       </c>
       <c r="E37">
-        <v>9772</v>
+        <v>5690</v>
       </c>
       <c r="F37" t="str">
         <v>Pendente</v>
@@ -1509,7 +1762,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>Cleci</v>
+        <v>Ivan Pedro Freitas</v>
       </c>
       <c r="C38" t="str">
         <v>Adulto</v>
@@ -1518,13 +1771,13 @@
         <v/>
       </c>
       <c r="E38">
-        <v>9772</v>
+        <v>1001</v>
       </c>
       <c r="F38" t="str">
         <v>Pendente</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>29/04/2025</v>
       </c>
     </row>
     <row r="39">
@@ -1532,7 +1785,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>Yasmin</v>
+        <v>Erick Almeida</v>
       </c>
       <c r="C39" t="str">
         <v>Adulto</v>
@@ -1541,7 +1794,7 @@
         <v/>
       </c>
       <c r="E39">
-        <v>9772</v>
+        <v>9251</v>
       </c>
       <c r="F39" t="str">
         <v>Pendente</v>
@@ -1555,7 +1808,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>Paulete</v>
+        <v>Matheus</v>
       </c>
       <c r="C40" t="str">
         <v>Adulto</v>
@@ -1564,7 +1817,7 @@
         <v/>
       </c>
       <c r="E40">
-        <v>2978</v>
+        <v>9251</v>
       </c>
       <c r="F40" t="str">
         <v>Pendente</v>
@@ -1578,7 +1831,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>Isaura Monteiro</v>
+        <v>Caroline Farias</v>
       </c>
       <c r="C41" t="str">
         <v>Adulto</v>
@@ -1587,7 +1840,7 @@
         <v/>
       </c>
       <c r="E41">
-        <v>4666</v>
+        <v>8228</v>
       </c>
       <c r="F41" t="str">
         <v>Pendente</v>
@@ -1601,7 +1854,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>Vanessa Kissler</v>
+        <v>Marcelo Vergara</v>
       </c>
       <c r="C42" t="str">
         <v>Adulto</v>
@@ -1610,7 +1863,7 @@
         <v/>
       </c>
       <c r="E42">
-        <v>1228</v>
+        <v>8228</v>
       </c>
       <c r="F42" t="str">
         <v>Pendente</v>
@@ -1624,7 +1877,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>Guilherme Becker</v>
+        <v>Mateus Leote</v>
       </c>
       <c r="C43" t="str">
         <v>Adulto</v>
@@ -1633,7 +1886,7 @@
         <v/>
       </c>
       <c r="E43">
-        <v>1228</v>
+        <v>5990</v>
       </c>
       <c r="F43" t="str">
         <v>Pendente</v>
@@ -1647,7 +1900,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>Maria Eduarda Rocha</v>
+        <v>Julia Cardoso</v>
       </c>
       <c r="C44" t="str">
         <v>Adulto</v>
@@ -1656,7 +1909,7 @@
         <v/>
       </c>
       <c r="E44">
-        <v>5690</v>
+        <v>5990</v>
       </c>
       <c r="F44" t="str">
         <v>Pendente</v>
@@ -1670,7 +1923,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>Ivan</v>
+        <v>Sara Rubia</v>
       </c>
       <c r="C45" t="str">
         <v>Adulto</v>
@@ -1679,7 +1932,7 @@
         <v/>
       </c>
       <c r="E45">
-        <v>5690</v>
+        <v>8326</v>
       </c>
       <c r="F45" t="str">
         <v>Pendente</v>
@@ -1693,7 +1946,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>Ivan Pedro Freitas</v>
+        <v>Eduarda Leal</v>
       </c>
       <c r="C46" t="str">
         <v>Adulto</v>
@@ -1702,13 +1955,13 @@
         <v/>
       </c>
       <c r="E46">
-        <v>1001</v>
+        <v>3277</v>
       </c>
       <c r="F46" t="str">
         <v>Pendente</v>
       </c>
       <c r="G46" t="str">
-        <v>29/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -1716,7 +1969,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>Erick Almeida</v>
+        <v>Gabriela</v>
       </c>
       <c r="C47" t="str">
         <v>Adulto</v>
@@ -1725,7 +1978,7 @@
         <v/>
       </c>
       <c r="E47">
-        <v>9251</v>
+        <v>7792</v>
       </c>
       <c r="F47" t="str">
         <v>Pendente</v>
@@ -1739,7 +1992,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Matheus</v>
+        <v>Eduardo Viegas</v>
       </c>
       <c r="C48" t="str">
         <v>Adulto</v>
@@ -1748,7 +2001,7 @@
         <v/>
       </c>
       <c r="E48">
-        <v>9251</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="str">
         <v>Pendente</v>
@@ -1762,7 +2015,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>Guilherme Mocelin</v>
+        <v>Gabriele Knop</v>
       </c>
       <c r="C49" t="str">
         <v>Adulto</v>
@@ -1771,13 +2024,13 @@
         <v/>
       </c>
       <c r="E49">
-        <v>9871</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="str">
         <v>Pendente</v>
       </c>
       <c r="G49" t="str">
-        <v>20/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -1785,7 +2038,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>Caroline Farias</v>
+        <v>Eduardo Kern</v>
       </c>
       <c r="C50" t="str">
         <v>Adulto</v>
@@ -1794,7 +2047,7 @@
         <v/>
       </c>
       <c r="E50">
-        <v>8228</v>
+        <v>8504</v>
       </c>
       <c r="F50" t="str">
         <v>Pendente</v>
@@ -1808,7 +2061,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Marcelo Vergara</v>
+        <v>Henrique Demarchi</v>
       </c>
       <c r="C51" t="str">
         <v>Adulto</v>
@@ -1817,13 +2070,13 @@
         <v/>
       </c>
       <c r="E51">
-        <v>8228</v>
+        <v>2036</v>
       </c>
       <c r="F51" t="str">
         <v>Pendente</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>04/05/2025</v>
       </c>
     </row>
     <row r="52">
@@ -1831,7 +2084,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>Mateus Leote</v>
+        <v>Franciele de Leon</v>
       </c>
       <c r="C52" t="str">
         <v>Adulto</v>
@@ -1840,7 +2093,7 @@
         <v/>
       </c>
       <c r="E52">
-        <v>5990</v>
+        <v>8778</v>
       </c>
       <c r="F52" t="str">
         <v>Pendente</v>
@@ -1854,7 +2107,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>Julia Cardoso</v>
+        <v>Bruno Erling</v>
       </c>
       <c r="C53" t="str">
         <v>Adulto</v>
@@ -1863,7 +2116,7 @@
         <v/>
       </c>
       <c r="E53">
-        <v>5990</v>
+        <v>8778</v>
       </c>
       <c r="F53" t="str">
         <v>Pendente</v>
@@ -1877,7 +2130,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>Sara Rubia</v>
+        <v>Sandriele de Leon</v>
       </c>
       <c r="C54" t="str">
         <v>Adulto</v>
@@ -1886,7 +2139,7 @@
         <v/>
       </c>
       <c r="E54">
-        <v>8326</v>
+        <v>4142</v>
       </c>
       <c r="F54" t="str">
         <v>Pendente</v>
@@ -1900,7 +2153,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>Eduarda Leal</v>
+        <v>Giuvanni Bagatini</v>
       </c>
       <c r="C55" t="str">
         <v>Adulto</v>
@@ -1909,7 +2162,7 @@
         <v/>
       </c>
       <c r="E55">
-        <v>3277</v>
+        <v>4142</v>
       </c>
       <c r="F55" t="str">
         <v>Pendente</v>
@@ -1923,7 +2176,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>Gabriela</v>
+        <v>Rochele de Leon</v>
       </c>
       <c r="C56" t="str">
         <v>Adulto</v>
@@ -1932,7 +2185,7 @@
         <v/>
       </c>
       <c r="E56">
-        <v>7792</v>
+        <v>3163</v>
       </c>
       <c r="F56" t="str">
         <v>Pendente</v>
@@ -1946,7 +2199,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>Eduardo Viegas</v>
+        <v>Sandro Marques</v>
       </c>
       <c r="C57" t="str">
         <v>Adulto</v>
@@ -1955,7 +2208,7 @@
         <v/>
       </c>
       <c r="E57">
-        <v>5447</v>
+        <v>3163</v>
       </c>
       <c r="F57" t="str">
         <v>Pendente</v>
@@ -1969,7 +2222,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>Gabriele Knop</v>
+        <v>Cleusa</v>
       </c>
       <c r="C58" t="str">
         <v>Adulto</v>
@@ -1978,7 +2231,7 @@
         <v/>
       </c>
       <c r="E58">
-        <v>5447</v>
+        <v>6684</v>
       </c>
       <c r="F58" t="str">
         <v>Pendente</v>
@@ -1992,7 +2245,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>Eduardo Kern</v>
+        <v>Luiz Airton</v>
       </c>
       <c r="C59" t="str">
         <v>Adulto</v>
@@ -2001,7 +2254,7 @@
         <v/>
       </c>
       <c r="E59">
-        <v>8504</v>
+        <v>6684</v>
       </c>
       <c r="F59" t="str">
         <v>Pendente</v>
@@ -2015,7 +2268,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>Henrique Demarchi</v>
+        <v>Angela</v>
       </c>
       <c r="C60" t="str">
         <v>Adulto</v>
@@ -2024,13 +2277,13 @@
         <v/>
       </c>
       <c r="E60">
-        <v>2036</v>
+        <v>9860</v>
       </c>
       <c r="F60" t="str">
         <v>Pendente</v>
       </c>
       <c r="G60" t="str">
-        <v>04/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -2038,7 +2291,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Franciele de Leon</v>
+        <v>Alexandre</v>
       </c>
       <c r="C61" t="str">
         <v>Adulto</v>
@@ -2047,7 +2300,7 @@
         <v/>
       </c>
       <c r="E61">
-        <v>8778</v>
+        <v>9860</v>
       </c>
       <c r="F61" t="str">
         <v>Pendente</v>
@@ -2061,7 +2314,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Bruno Erling</v>
+        <v>Amanda</v>
       </c>
       <c r="C62" t="str">
         <v>Adulto</v>
@@ -2070,13 +2323,13 @@
         <v/>
       </c>
       <c r="E62">
-        <v>8778</v>
+        <v>1558</v>
       </c>
       <c r="F62" t="str">
         <v>Pendente</v>
       </c>
       <c r="G62" t="str">
-        <v/>
+        <v>19/04/2025</v>
       </c>
     </row>
     <row r="63">
@@ -2084,7 +2337,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Sandriele de Leon</v>
+        <v>Giuliano</v>
       </c>
       <c r="C63" t="str">
         <v>Adulto</v>
@@ -2093,13 +2346,13 @@
         <v/>
       </c>
       <c r="E63">
-        <v>4142</v>
+        <v>1558</v>
       </c>
       <c r="F63" t="str">
         <v>Pendente</v>
       </c>
       <c r="G63" t="str">
-        <v/>
+        <v>19/04/2025</v>
       </c>
     </row>
     <row r="64">
@@ -2107,7 +2360,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>Giuvanni Bagatini</v>
+        <v>Natalia</v>
       </c>
       <c r="C64" t="str">
         <v>Adulto</v>
@@ -2116,7 +2369,7 @@
         <v/>
       </c>
       <c r="E64">
-        <v>4142</v>
+        <v>8602</v>
       </c>
       <c r="F64" t="str">
         <v>Pendente</v>
@@ -2130,7 +2383,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Rochele de Leon</v>
+        <v>Guilherme Lobo</v>
       </c>
       <c r="C65" t="str">
         <v>Adulto</v>
@@ -2139,7 +2392,7 @@
         <v/>
       </c>
       <c r="E65">
-        <v>3163</v>
+        <v>8602</v>
       </c>
       <c r="F65" t="str">
         <v>Pendente</v>
@@ -2153,16 +2406,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Sandro Marques</v>
+        <v>Daniel</v>
       </c>
       <c r="C66" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D66" t="str">
         <v/>
       </c>
       <c r="E66">
-        <v>3163</v>
+        <v>5124</v>
       </c>
       <c r="F66" t="str">
         <v>Pendente</v>
@@ -2176,16 +2429,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>Cleusa</v>
+        <v>Lorenzo</v>
       </c>
       <c r="C67" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D67" t="str">
         <v/>
       </c>
       <c r="E67">
-        <v>6684</v>
+        <v>4142</v>
       </c>
       <c r="F67" t="str">
         <v>Pendente</v>
@@ -2199,16 +2452,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>Luiz Airton</v>
+        <v>Julia</v>
       </c>
       <c r="C68" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D68" t="str">
         <v/>
       </c>
       <c r="E68">
-        <v>6684</v>
+        <v>5124</v>
       </c>
       <c r="F68" t="str">
         <v>Pendente</v>
@@ -2222,16 +2475,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>Angela</v>
+        <v>Julia Erling</v>
       </c>
       <c r="C69" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D69" t="str">
         <v/>
       </c>
       <c r="E69">
-        <v>9860</v>
+        <v>8778</v>
       </c>
       <c r="F69" t="str">
         <v>Pendente</v>
@@ -2245,16 +2498,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>Alexandre</v>
+        <v>Theo</v>
       </c>
       <c r="C70" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D70" t="str">
         <v/>
       </c>
       <c r="E70">
-        <v>9860</v>
+        <v>8602</v>
       </c>
       <c r="F70" t="str">
         <v>Pendente</v>
@@ -2268,10 +2521,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>Amanda</v>
+        <v>Antonio</v>
       </c>
       <c r="C71" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -2291,7 +2544,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>Giuliano</v>
+        <v>Rafael Dutra</v>
       </c>
       <c r="C72" t="str">
         <v>Adulto</v>
@@ -2300,13 +2553,13 @@
         <v/>
       </c>
       <c r="E72">
-        <v>1558</v>
+        <v>7947</v>
       </c>
       <c r="F72" t="str">
         <v>Pendente</v>
       </c>
       <c r="G72" t="str">
-        <v>19/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -2314,7 +2567,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>Natalia</v>
+        <v>Hérica Marques</v>
       </c>
       <c r="C73" t="str">
         <v>Adulto</v>
@@ -2323,7 +2576,7 @@
         <v/>
       </c>
       <c r="E73">
-        <v>8602</v>
+        <v>8284</v>
       </c>
       <c r="F73" t="str">
         <v>Pendente</v>
@@ -2337,7 +2590,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>Guilherme Lobo</v>
+        <v>Thomas</v>
       </c>
       <c r="C74" t="str">
         <v>Adulto</v>
@@ -2346,7 +2599,7 @@
         <v/>
       </c>
       <c r="E74">
-        <v>8602</v>
+        <v>8284</v>
       </c>
       <c r="F74" t="str">
         <v>Pendente</v>
@@ -2360,7 +2613,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>Daniel</v>
+        <v>Gustavo</v>
       </c>
       <c r="C75" t="str">
         <v>CRIANCA</v>
@@ -2369,7 +2622,7 @@
         <v/>
       </c>
       <c r="E75">
-        <v>5124</v>
+        <v>8284</v>
       </c>
       <c r="F75" t="str">
         <v>Pendente</v>
@@ -2383,7 +2636,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>Lorenzo</v>
+        <v>Guilherme</v>
       </c>
       <c r="C76" t="str">
         <v>CRIANCA</v>
@@ -2392,7 +2645,7 @@
         <v/>
       </c>
       <c r="E76">
-        <v>4142</v>
+        <v>8284</v>
       </c>
       <c r="F76" t="str">
         <v>Pendente</v>
@@ -2406,7 +2659,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>Julia</v>
+        <v>Sofia</v>
       </c>
       <c r="C77" t="str">
         <v>CRIANCA</v>
@@ -2415,7 +2668,7 @@
         <v/>
       </c>
       <c r="E77">
-        <v>5124</v>
+        <v>8284</v>
       </c>
       <c r="F77" t="str">
         <v>Pendente</v>
@@ -2429,257 +2682,27 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>Julia Erling</v>
+        <v>João Pedro Marçal</v>
       </c>
       <c r="C78" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D78" t="str">
         <v/>
       </c>
       <c r="E78">
-        <v>8778</v>
+        <v>2036</v>
       </c>
       <c r="F78" t="str">
         <v>Pendente</v>
       </c>
       <c r="G78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="str">
-        <v>Theo</v>
-      </c>
-      <c r="C79" t="str">
-        <v>CRIANCA</v>
-      </c>
-      <c r="D79" t="str">
-        <v/>
-      </c>
-      <c r="E79">
-        <v>8602</v>
-      </c>
-      <c r="F79" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Luisa Silva</v>
-      </c>
-      <c r="C80" t="str">
-        <v>CRIANCA</v>
-      </c>
-      <c r="D80" t="str">
-        <v/>
-      </c>
-      <c r="E80">
-        <v>4417</v>
-      </c>
-      <c r="F80" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="str">
-        <v>Antonio</v>
-      </c>
-      <c r="C81" t="str">
-        <v>CRIANCA</v>
-      </c>
-      <c r="D81" t="str">
-        <v/>
-      </c>
-      <c r="E81">
-        <v>1558</v>
-      </c>
-      <c r="F81" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G81" t="str">
-        <v>19/04/2025</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="str">
-        <v>Rafael Dutra</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D82" t="str">
-        <v/>
-      </c>
-      <c r="E82">
-        <v>7947</v>
-      </c>
-      <c r="F82" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="str">
-        <v>Hérica Marques</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D83" t="str">
-        <v/>
-      </c>
-      <c r="E83">
-        <v>8284</v>
-      </c>
-      <c r="F83" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G83" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Thomas</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D84" t="str">
-        <v/>
-      </c>
-      <c r="E84">
-        <v>8284</v>
-      </c>
-      <c r="F84" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Gustavo</v>
-      </c>
-      <c r="C85" t="str">
-        <v>CRIANCA</v>
-      </c>
-      <c r="D85" t="str">
-        <v/>
-      </c>
-      <c r="E85">
-        <v>8284</v>
-      </c>
-      <c r="F85" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Guilherme</v>
-      </c>
-      <c r="C86" t="str">
-        <v>CRIANCA</v>
-      </c>
-      <c r="D86" t="str">
-        <v/>
-      </c>
-      <c r="E86">
-        <v>8284</v>
-      </c>
-      <c r="F86" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Sofia</v>
-      </c>
-      <c r="C87" t="str">
-        <v>CRIANCA</v>
-      </c>
-      <c r="D87" t="str">
-        <v/>
-      </c>
-      <c r="E87">
-        <v>8284</v>
-      </c>
-      <c r="F87" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="str">
-        <v>João Pedro Marçal</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D88" t="str">
-        <v/>
-      </c>
-      <c r="E88">
-        <v>2036</v>
-      </c>
-      <c r="F88" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G88" t="str">
         <v>04/05/2025</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G88"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G78"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2713,25 +2736,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/graduation-api/convidados_confirmados.xlsx
+++ b/graduation-api/convidados_confirmados.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -494,400 +494,9 @@
         <v>15/05/2025</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Lucas Silva</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5">
-        <v>3261</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G5" t="str">
-        <v>13/05/2025</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Sabrina Roani</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6">
-        <v>3261</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G6" t="str">
-        <v>13/05/2025</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Sandra Silva</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7">
-        <v>6744</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G7" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Antônio Renê Silva</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
-        <v>6744</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G8" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Nicole Silva</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
-        <v>2580</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G9" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Pedro Tremarin</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10">
-        <v>2580</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G10" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>João Paulo Silva</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11">
-        <v>4417</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G11" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Vanessa Brum</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12">
-        <v>4417</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G12" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Leonardo Brum</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13">
-        <v>4417</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G13" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Maria Silva</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14">
-        <v>2550</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G14" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="str">
-        <v>João Batista</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15">
-        <v>3261</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G15" t="str">
-        <v>13/05/2025</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Guilherme Mocelin</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16">
-        <v>9871</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G16" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Luisa Silva</v>
-      </c>
-      <c r="C17" t="str">
-        <v>CRIANCA (7 anos)</v>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
-      <c r="E17">
-        <v>4417</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G17" t="str">
-        <v>14/05/2025</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Benjamin Silva</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18">
-        <v>3261</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G18" t="str">
-        <v>13/05/2025</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Benicio Silva</v>
-      </c>
-      <c r="C19" t="str">
-        <v>CRIANCA (10 anos)</v>
-      </c>
-      <c r="D19">
-        <v>10</v>
-      </c>
-      <c r="E19">
-        <v>3261</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G19" t="str">
-        <v>13/05/2025</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Joaquim Silva</v>
-      </c>
-      <c r="C20" t="str">
-        <v>CRIANCA (8 anos)</v>
-      </c>
-      <c r="D20">
-        <v>8</v>
-      </c>
-      <c r="E20">
-        <v>3261</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G20" t="str">
-        <v>13/05/2025</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Teste</v>
-      </c>
-      <c r="C21" t="str">
-        <v>CRIANCA (2 anos)</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>1240</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Confirmado</v>
-      </c>
-      <c r="G21" t="str">
-        <v>15/05/2025</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -904,7 +513,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -934,7 +543,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Ísis Silva</v>
+        <v>Lucas Silva</v>
       </c>
       <c r="C2" t="str">
         <v>Adulto</v>
@@ -943,7 +552,7 @@
         <v/>
       </c>
       <c r="E2">
-        <v>6612</v>
+        <v>3261</v>
       </c>
       <c r="F2" t="str">
         <v>Pendente</v>
@@ -957,7 +566,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Graça Teresinha</v>
+        <v>Sabrina Roani</v>
       </c>
       <c r="C3" t="str">
         <v>Adulto</v>
@@ -966,7 +575,7 @@
         <v/>
       </c>
       <c r="E3">
-        <v>1754</v>
+        <v>3261</v>
       </c>
       <c r="F3" t="str">
         <v>Pendente</v>
@@ -980,7 +589,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Renato</v>
+        <v>Sandra Silva</v>
       </c>
       <c r="C4" t="str">
         <v>Adulto</v>
@@ -989,7 +598,7 @@
         <v/>
       </c>
       <c r="E4">
-        <v>1754</v>
+        <v>6744</v>
       </c>
       <c r="F4" t="str">
         <v>Pendente</v>
@@ -1003,7 +612,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Cheila Machado</v>
+        <v>Antônio Renê Silva</v>
       </c>
       <c r="C5" t="str">
         <v>Adulto</v>
@@ -1012,7 +621,7 @@
         <v/>
       </c>
       <c r="E5">
-        <v>5820</v>
+        <v>6744</v>
       </c>
       <c r="F5" t="str">
         <v>Pendente</v>
@@ -1026,7 +635,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Paulo Machado</v>
+        <v>Nicole Silva</v>
       </c>
       <c r="C6" t="str">
         <v>Adulto</v>
@@ -1035,7 +644,7 @@
         <v/>
       </c>
       <c r="E6">
-        <v>5820</v>
+        <v>2580</v>
       </c>
       <c r="F6" t="str">
         <v>Pendente</v>
@@ -1049,7 +658,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Gustavo Machado</v>
+        <v>Pedro Tremarin</v>
       </c>
       <c r="C7" t="str">
         <v>Adulto</v>
@@ -1058,7 +667,7 @@
         <v/>
       </c>
       <c r="E7">
-        <v>5820</v>
+        <v>2580</v>
       </c>
       <c r="F7" t="str">
         <v>Pendente</v>
@@ -1072,7 +681,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Yasmin Teixeira</v>
+        <v>João Paulo Silva</v>
       </c>
       <c r="C8" t="str">
         <v>Adulto</v>
@@ -1081,7 +690,7 @@
         <v/>
       </c>
       <c r="E8">
-        <v>5820</v>
+        <v>4417</v>
       </c>
       <c r="F8" t="str">
         <v>Pendente</v>
@@ -1095,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Arthur Machado</v>
+        <v>Vanessa Brum</v>
       </c>
       <c r="C9" t="str">
         <v>Adulto</v>
@@ -1104,7 +713,7 @@
         <v/>
       </c>
       <c r="E9">
-        <v>5820</v>
+        <v>4417</v>
       </c>
       <c r="F9" t="str">
         <v>Pendente</v>
@@ -1118,7 +727,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Rafaella Buttenbender</v>
+        <v>Leonardo Brum</v>
       </c>
       <c r="C10" t="str">
         <v>Adulto</v>
@@ -1127,7 +736,7 @@
         <v/>
       </c>
       <c r="E10">
-        <v>5820</v>
+        <v>4417</v>
       </c>
       <c r="F10" t="str">
         <v>Pendente</v>
@@ -1141,7 +750,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Vilson</v>
+        <v>Maria Silva</v>
       </c>
       <c r="C11" t="str">
         <v>Adulto</v>
@@ -1150,7 +759,7 @@
         <v/>
       </c>
       <c r="E11">
-        <v>7361</v>
+        <v>2550</v>
       </c>
       <c r="F11" t="str">
         <v>Pendente</v>
@@ -1164,7 +773,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Rita</v>
+        <v>Ísis Silva</v>
       </c>
       <c r="C12" t="str">
         <v>Adulto</v>
@@ -1173,7 +782,7 @@
         <v/>
       </c>
       <c r="E12">
-        <v>7361</v>
+        <v>6612</v>
       </c>
       <c r="F12" t="str">
         <v>Pendente</v>
@@ -1187,7 +796,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Rose</v>
+        <v>João Batista</v>
       </c>
       <c r="C13" t="str">
         <v>Adulto</v>
@@ -1196,7 +805,7 @@
         <v/>
       </c>
       <c r="E13">
-        <v>1636</v>
+        <v>3261</v>
       </c>
       <c r="F13" t="str">
         <v>Pendente</v>
@@ -1210,7 +819,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Ronei</v>
+        <v>Graça Teresinha</v>
       </c>
       <c r="C14" t="str">
         <v>Adulto</v>
@@ -1219,7 +828,7 @@
         <v/>
       </c>
       <c r="E14">
-        <v>1636</v>
+        <v>1754</v>
       </c>
       <c r="F14" t="str">
         <v>Pendente</v>
@@ -1233,7 +842,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Volmar Machado</v>
+        <v>Renato</v>
       </c>
       <c r="C15" t="str">
         <v>Adulto</v>
@@ -1242,7 +851,7 @@
         <v/>
       </c>
       <c r="E15">
-        <v>8234</v>
+        <v>1754</v>
       </c>
       <c r="F15" t="str">
         <v>Pendente</v>
@@ -1256,7 +865,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Lurdes</v>
+        <v>Cheila Machado</v>
       </c>
       <c r="C16" t="str">
         <v>Adulto</v>
@@ -1265,7 +874,7 @@
         <v/>
       </c>
       <c r="E16">
-        <v>2222</v>
+        <v>5820</v>
       </c>
       <c r="F16" t="str">
         <v>Pendente</v>
@@ -1279,7 +888,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Cecinha</v>
+        <v>Paulo Machado</v>
       </c>
       <c r="C17" t="str">
         <v>Adulto</v>
@@ -1288,7 +897,7 @@
         <v/>
       </c>
       <c r="E17">
-        <v>3333</v>
+        <v>5820</v>
       </c>
       <c r="F17" t="str">
         <v>Pendente</v>
@@ -1302,7 +911,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Claudete Freitas</v>
+        <v>Gustavo Machado</v>
       </c>
       <c r="C18" t="str">
         <v>Adulto</v>
@@ -1311,7 +920,7 @@
         <v/>
       </c>
       <c r="E18">
-        <v>8990</v>
+        <v>5820</v>
       </c>
       <c r="F18" t="str">
         <v>Pendente</v>
@@ -1325,7 +934,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Elizabeth</v>
+        <v>Yasmin Teixeira</v>
       </c>
       <c r="C19" t="str">
         <v>Adulto</v>
@@ -1334,7 +943,7 @@
         <v/>
       </c>
       <c r="E19">
-        <v>8990</v>
+        <v>5820</v>
       </c>
       <c r="F19" t="str">
         <v>Pendente</v>
@@ -1348,7 +957,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Lucas Garcia</v>
+        <v>Arthur Machado</v>
       </c>
       <c r="C20" t="str">
         <v>Adulto</v>
@@ -1357,7 +966,7 @@
         <v/>
       </c>
       <c r="E20">
-        <v>2558</v>
+        <v>5820</v>
       </c>
       <c r="F20" t="str">
         <v>Pendente</v>
@@ -1371,7 +980,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Monique</v>
+        <v>Rafaella Buttenbender</v>
       </c>
       <c r="C21" t="str">
         <v>Adulto</v>
@@ -1380,7 +989,7 @@
         <v/>
       </c>
       <c r="E21">
-        <v>2558</v>
+        <v>5820</v>
       </c>
       <c r="F21" t="str">
         <v>Pendente</v>
@@ -1394,7 +1003,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Ivonete</v>
+        <v>Vilson</v>
       </c>
       <c r="C22" t="str">
         <v>Adulto</v>
@@ -1403,7 +1012,7 @@
         <v/>
       </c>
       <c r="E22">
-        <v>5555</v>
+        <v>7361</v>
       </c>
       <c r="F22" t="str">
         <v>Pendente</v>
@@ -1417,7 +1026,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Einar Marques</v>
+        <v>Rita</v>
       </c>
       <c r="C23" t="str">
         <v>Adulto</v>
@@ -1426,7 +1035,7 @@
         <v/>
       </c>
       <c r="E23">
-        <v>5496</v>
+        <v>7361</v>
       </c>
       <c r="F23" t="str">
         <v>Pendente</v>
@@ -1440,7 +1049,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Fabiana Gomes</v>
+        <v>Rose</v>
       </c>
       <c r="C24" t="str">
         <v>Adulto</v>
@@ -1449,7 +1058,7 @@
         <v/>
       </c>
       <c r="E24">
-        <v>5496</v>
+        <v>1636</v>
       </c>
       <c r="F24" t="str">
         <v>Pendente</v>
@@ -1463,7 +1072,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Marco Martins</v>
+        <v>Ronei</v>
       </c>
       <c r="C25" t="str">
         <v>Adulto</v>
@@ -1472,7 +1081,7 @@
         <v/>
       </c>
       <c r="E25">
-        <v>5001</v>
+        <v>1636</v>
       </c>
       <c r="F25" t="str">
         <v>Pendente</v>
@@ -1486,7 +1095,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Rose Tormann</v>
+        <v>Volmar Machado</v>
       </c>
       <c r="C26" t="str">
         <v>Adulto</v>
@@ -1495,7 +1104,7 @@
         <v/>
       </c>
       <c r="E26">
-        <v>5001</v>
+        <v>8234</v>
       </c>
       <c r="F26" t="str">
         <v>Pendente</v>
@@ -1509,7 +1118,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>Júlio</v>
+        <v>Lurdes</v>
       </c>
       <c r="C27" t="str">
         <v>Adulto</v>
@@ -1518,7 +1127,7 @@
         <v/>
       </c>
       <c r="E27">
-        <v>5124</v>
+        <v>2222</v>
       </c>
       <c r="F27" t="str">
         <v>Pendente</v>
@@ -1532,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Jocasta</v>
+        <v>Cecinha</v>
       </c>
       <c r="C28" t="str">
         <v>Adulto</v>
@@ -1541,7 +1150,7 @@
         <v/>
       </c>
       <c r="E28">
-        <v>5124</v>
+        <v>3333</v>
       </c>
       <c r="F28" t="str">
         <v>Pendente</v>
@@ -1555,7 +1164,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Fábio</v>
+        <v>Claudete Freitas</v>
       </c>
       <c r="C29" t="str">
         <v>Adulto</v>
@@ -1564,7 +1173,7 @@
         <v/>
       </c>
       <c r="E29">
-        <v>9772</v>
+        <v>8990</v>
       </c>
       <c r="F29" t="str">
         <v>Pendente</v>
@@ -1578,7 +1187,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Cleci</v>
+        <v>Elizabeth</v>
       </c>
       <c r="C30" t="str">
         <v>Adulto</v>
@@ -1587,7 +1196,7 @@
         <v/>
       </c>
       <c r="E30">
-        <v>9772</v>
+        <v>8990</v>
       </c>
       <c r="F30" t="str">
         <v>Pendente</v>
@@ -1601,7 +1210,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Yasmin</v>
+        <v>Lucas Garcia</v>
       </c>
       <c r="C31" t="str">
         <v>Adulto</v>
@@ -1610,7 +1219,7 @@
         <v/>
       </c>
       <c r="E31">
-        <v>9772</v>
+        <v>2558</v>
       </c>
       <c r="F31" t="str">
         <v>Pendente</v>
@@ -1624,7 +1233,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>Paulete</v>
+        <v>Monique</v>
       </c>
       <c r="C32" t="str">
         <v>Adulto</v>
@@ -1633,7 +1242,7 @@
         <v/>
       </c>
       <c r="E32">
-        <v>2978</v>
+        <v>2558</v>
       </c>
       <c r="F32" t="str">
         <v>Pendente</v>
@@ -1647,7 +1256,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>Isaura Monteiro</v>
+        <v>Ivonete</v>
       </c>
       <c r="C33" t="str">
         <v>Adulto</v>
@@ -1656,7 +1265,7 @@
         <v/>
       </c>
       <c r="E33">
-        <v>4666</v>
+        <v>5555</v>
       </c>
       <c r="F33" t="str">
         <v>Pendente</v>
@@ -1670,7 +1279,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>Vanessa Kissler</v>
+        <v>Einar Marques</v>
       </c>
       <c r="C34" t="str">
         <v>Adulto</v>
@@ -1679,7 +1288,7 @@
         <v/>
       </c>
       <c r="E34">
-        <v>1228</v>
+        <v>5496</v>
       </c>
       <c r="F34" t="str">
         <v>Pendente</v>
@@ -1693,7 +1302,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>Guilherme Becker</v>
+        <v>Fabiana Gomes</v>
       </c>
       <c r="C35" t="str">
         <v>Adulto</v>
@@ -1702,7 +1311,7 @@
         <v/>
       </c>
       <c r="E35">
-        <v>1228</v>
+        <v>5496</v>
       </c>
       <c r="F35" t="str">
         <v>Pendente</v>
@@ -1716,7 +1325,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>Maria Eduarda Rocha</v>
+        <v>Marco Martins</v>
       </c>
       <c r="C36" t="str">
         <v>Adulto</v>
@@ -1725,7 +1334,7 @@
         <v/>
       </c>
       <c r="E36">
-        <v>5690</v>
+        <v>5001</v>
       </c>
       <c r="F36" t="str">
         <v>Pendente</v>
@@ -1739,7 +1348,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>Ivan</v>
+        <v>Rose Tormann</v>
       </c>
       <c r="C37" t="str">
         <v>Adulto</v>
@@ -1748,7 +1357,7 @@
         <v/>
       </c>
       <c r="E37">
-        <v>5690</v>
+        <v>5001</v>
       </c>
       <c r="F37" t="str">
         <v>Pendente</v>
@@ -1762,7 +1371,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>Ivan Pedro Freitas</v>
+        <v>Júlio</v>
       </c>
       <c r="C38" t="str">
         <v>Adulto</v>
@@ -1771,13 +1380,13 @@
         <v/>
       </c>
       <c r="E38">
-        <v>1001</v>
+        <v>5124</v>
       </c>
       <c r="F38" t="str">
         <v>Pendente</v>
       </c>
       <c r="G38" t="str">
-        <v>29/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1785,7 +1394,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>Erick Almeida</v>
+        <v>Jocasta</v>
       </c>
       <c r="C39" t="str">
         <v>Adulto</v>
@@ -1794,7 +1403,7 @@
         <v/>
       </c>
       <c r="E39">
-        <v>9251</v>
+        <v>5124</v>
       </c>
       <c r="F39" t="str">
         <v>Pendente</v>
@@ -1808,7 +1417,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>Matheus</v>
+        <v>Fábio</v>
       </c>
       <c r="C40" t="str">
         <v>Adulto</v>
@@ -1817,7 +1426,7 @@
         <v/>
       </c>
       <c r="E40">
-        <v>9251</v>
+        <v>9772</v>
       </c>
       <c r="F40" t="str">
         <v>Pendente</v>
@@ -1831,7 +1440,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>Caroline Farias</v>
+        <v>Cleci</v>
       </c>
       <c r="C41" t="str">
         <v>Adulto</v>
@@ -1840,7 +1449,7 @@
         <v/>
       </c>
       <c r="E41">
-        <v>8228</v>
+        <v>9772</v>
       </c>
       <c r="F41" t="str">
         <v>Pendente</v>
@@ -1854,7 +1463,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>Marcelo Vergara</v>
+        <v>Yasmin</v>
       </c>
       <c r="C42" t="str">
         <v>Adulto</v>
@@ -1863,7 +1472,7 @@
         <v/>
       </c>
       <c r="E42">
-        <v>8228</v>
+        <v>9772</v>
       </c>
       <c r="F42" t="str">
         <v>Pendente</v>
@@ -1877,7 +1486,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>Mateus Leote</v>
+        <v>Paulete</v>
       </c>
       <c r="C43" t="str">
         <v>Adulto</v>
@@ -1886,7 +1495,7 @@
         <v/>
       </c>
       <c r="E43">
-        <v>5990</v>
+        <v>2978</v>
       </c>
       <c r="F43" t="str">
         <v>Pendente</v>
@@ -1900,7 +1509,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>Julia Cardoso</v>
+        <v>Isaura Monteiro</v>
       </c>
       <c r="C44" t="str">
         <v>Adulto</v>
@@ -1909,7 +1518,7 @@
         <v/>
       </c>
       <c r="E44">
-        <v>5990</v>
+        <v>4666</v>
       </c>
       <c r="F44" t="str">
         <v>Pendente</v>
@@ -1923,7 +1532,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>Sara Rubia</v>
+        <v>Vanessa Kissler</v>
       </c>
       <c r="C45" t="str">
         <v>Adulto</v>
@@ -1932,7 +1541,7 @@
         <v/>
       </c>
       <c r="E45">
-        <v>8326</v>
+        <v>1228</v>
       </c>
       <c r="F45" t="str">
         <v>Pendente</v>
@@ -1946,7 +1555,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>Eduarda Leal</v>
+        <v>Guilherme Becker</v>
       </c>
       <c r="C46" t="str">
         <v>Adulto</v>
@@ -1955,7 +1564,7 @@
         <v/>
       </c>
       <c r="E46">
-        <v>3277</v>
+        <v>1228</v>
       </c>
       <c r="F46" t="str">
         <v>Pendente</v>
@@ -1969,7 +1578,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>Gabriela</v>
+        <v>Maria Eduarda Rocha</v>
       </c>
       <c r="C47" t="str">
         <v>Adulto</v>
@@ -1978,7 +1587,7 @@
         <v/>
       </c>
       <c r="E47">
-        <v>7792</v>
+        <v>5690</v>
       </c>
       <c r="F47" t="str">
         <v>Pendente</v>
@@ -1992,7 +1601,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Eduardo Viegas</v>
+        <v>Ivan</v>
       </c>
       <c r="C48" t="str">
         <v>Adulto</v>
@@ -2001,7 +1610,7 @@
         <v/>
       </c>
       <c r="E48">
-        <v>5447</v>
+        <v>5690</v>
       </c>
       <c r="F48" t="str">
         <v>Pendente</v>
@@ -2015,7 +1624,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>Gabriele Knop</v>
+        <v>Ivan Pedro Freitas</v>
       </c>
       <c r="C49" t="str">
         <v>Adulto</v>
@@ -2024,7 +1633,7 @@
         <v/>
       </c>
       <c r="E49">
-        <v>5447</v>
+        <v>1001</v>
       </c>
       <c r="F49" t="str">
         <v>Pendente</v>
@@ -2038,7 +1647,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>Eduardo Kern</v>
+        <v>Erick Almeida</v>
       </c>
       <c r="C50" t="str">
         <v>Adulto</v>
@@ -2047,7 +1656,7 @@
         <v/>
       </c>
       <c r="E50">
-        <v>8504</v>
+        <v>9251</v>
       </c>
       <c r="F50" t="str">
         <v>Pendente</v>
@@ -2061,7 +1670,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Henrique Demarchi</v>
+        <v>Matheus</v>
       </c>
       <c r="C51" t="str">
         <v>Adulto</v>
@@ -2070,13 +1679,13 @@
         <v/>
       </c>
       <c r="E51">
-        <v>2036</v>
+        <v>9251</v>
       </c>
       <c r="F51" t="str">
         <v>Pendente</v>
       </c>
       <c r="G51" t="str">
-        <v>04/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -2084,7 +1693,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>Franciele de Leon</v>
+        <v>Guilherme Mocelin</v>
       </c>
       <c r="C52" t="str">
         <v>Adulto</v>
@@ -2093,7 +1702,7 @@
         <v/>
       </c>
       <c r="E52">
-        <v>8778</v>
+        <v>9871</v>
       </c>
       <c r="F52" t="str">
         <v>Pendente</v>
@@ -2107,7 +1716,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>Bruno Erling</v>
+        <v>Caroline Farias</v>
       </c>
       <c r="C53" t="str">
         <v>Adulto</v>
@@ -2116,7 +1725,7 @@
         <v/>
       </c>
       <c r="E53">
-        <v>8778</v>
+        <v>8228</v>
       </c>
       <c r="F53" t="str">
         <v>Pendente</v>
@@ -2130,7 +1739,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>Sandriele de Leon</v>
+        <v>Marcelo Vergara</v>
       </c>
       <c r="C54" t="str">
         <v>Adulto</v>
@@ -2139,7 +1748,7 @@
         <v/>
       </c>
       <c r="E54">
-        <v>4142</v>
+        <v>8228</v>
       </c>
       <c r="F54" t="str">
         <v>Pendente</v>
@@ -2153,7 +1762,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>Giuvanni Bagatini</v>
+        <v>Mateus Leote</v>
       </c>
       <c r="C55" t="str">
         <v>Adulto</v>
@@ -2162,7 +1771,7 @@
         <v/>
       </c>
       <c r="E55">
-        <v>4142</v>
+        <v>5990</v>
       </c>
       <c r="F55" t="str">
         <v>Pendente</v>
@@ -2176,7 +1785,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>Rochele de Leon</v>
+        <v>Julia Cardoso</v>
       </c>
       <c r="C56" t="str">
         <v>Adulto</v>
@@ -2185,7 +1794,7 @@
         <v/>
       </c>
       <c r="E56">
-        <v>3163</v>
+        <v>5990</v>
       </c>
       <c r="F56" t="str">
         <v>Pendente</v>
@@ -2199,7 +1808,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>Sandro Marques</v>
+        <v>Sara Rubia</v>
       </c>
       <c r="C57" t="str">
         <v>Adulto</v>
@@ -2208,7 +1817,7 @@
         <v/>
       </c>
       <c r="E57">
-        <v>3163</v>
+        <v>8326</v>
       </c>
       <c r="F57" t="str">
         <v>Pendente</v>
@@ -2222,7 +1831,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>Cleusa</v>
+        <v>Eduarda Leal</v>
       </c>
       <c r="C58" t="str">
         <v>Adulto</v>
@@ -2231,7 +1840,7 @@
         <v/>
       </c>
       <c r="E58">
-        <v>6684</v>
+        <v>3277</v>
       </c>
       <c r="F58" t="str">
         <v>Pendente</v>
@@ -2245,7 +1854,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>Luiz Airton</v>
+        <v>Gabriela</v>
       </c>
       <c r="C59" t="str">
         <v>Adulto</v>
@@ -2254,7 +1863,7 @@
         <v/>
       </c>
       <c r="E59">
-        <v>6684</v>
+        <v>7792</v>
       </c>
       <c r="F59" t="str">
         <v>Pendente</v>
@@ -2268,7 +1877,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>Angela</v>
+        <v>Eduardo Viegas</v>
       </c>
       <c r="C60" t="str">
         <v>Adulto</v>
@@ -2277,7 +1886,7 @@
         <v/>
       </c>
       <c r="E60">
-        <v>9860</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="str">
         <v>Pendente</v>
@@ -2291,7 +1900,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Alexandre</v>
+        <v>Gabriele Knop</v>
       </c>
       <c r="C61" t="str">
         <v>Adulto</v>
@@ -2300,7 +1909,7 @@
         <v/>
       </c>
       <c r="E61">
-        <v>9860</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="str">
         <v>Pendente</v>
@@ -2314,7 +1923,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Amanda</v>
+        <v>Eduardo Kern</v>
       </c>
       <c r="C62" t="str">
         <v>Adulto</v>
@@ -2323,13 +1932,13 @@
         <v/>
       </c>
       <c r="E62">
-        <v>1558</v>
+        <v>8504</v>
       </c>
       <c r="F62" t="str">
         <v>Pendente</v>
       </c>
       <c r="G62" t="str">
-        <v>19/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -2337,7 +1946,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Giuliano</v>
+        <v>Henrique Demarchi</v>
       </c>
       <c r="C63" t="str">
         <v>Adulto</v>
@@ -2346,13 +1955,13 @@
         <v/>
       </c>
       <c r="E63">
-        <v>1558</v>
+        <v>2036</v>
       </c>
       <c r="F63" t="str">
         <v>Pendente</v>
       </c>
       <c r="G63" t="str">
-        <v>19/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -2360,7 +1969,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>Natalia</v>
+        <v>Franciele de Leon</v>
       </c>
       <c r="C64" t="str">
         <v>Adulto</v>
@@ -2369,7 +1978,7 @@
         <v/>
       </c>
       <c r="E64">
-        <v>8602</v>
+        <v>8778</v>
       </c>
       <c r="F64" t="str">
         <v>Pendente</v>
@@ -2383,7 +1992,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Guilherme Lobo</v>
+        <v>Bruno Erling</v>
       </c>
       <c r="C65" t="str">
         <v>Adulto</v>
@@ -2392,7 +2001,7 @@
         <v/>
       </c>
       <c r="E65">
-        <v>8602</v>
+        <v>8778</v>
       </c>
       <c r="F65" t="str">
         <v>Pendente</v>
@@ -2406,16 +2015,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Daniel</v>
+        <v>Sandriele de Leon</v>
       </c>
       <c r="C66" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D66" t="str">
         <v/>
       </c>
       <c r="E66">
-        <v>5124</v>
+        <v>4142</v>
       </c>
       <c r="F66" t="str">
         <v>Pendente</v>
@@ -2429,10 +2038,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>Lorenzo</v>
+        <v>Giuvanni Bagatini</v>
       </c>
       <c r="C67" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D67" t="str">
         <v/>
@@ -2452,16 +2061,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>Julia</v>
+        <v>Rochele de Leon</v>
       </c>
       <c r="C68" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D68" t="str">
         <v/>
       </c>
       <c r="E68">
-        <v>5124</v>
+        <v>3163</v>
       </c>
       <c r="F68" t="str">
         <v>Pendente</v>
@@ -2475,16 +2084,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>Julia Erling</v>
+        <v>Sandro Marques</v>
       </c>
       <c r="C69" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D69" t="str">
         <v/>
       </c>
       <c r="E69">
-        <v>8778</v>
+        <v>3163</v>
       </c>
       <c r="F69" t="str">
         <v>Pendente</v>
@@ -2498,16 +2107,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>Theo</v>
+        <v>Cleusa</v>
       </c>
       <c r="C70" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D70" t="str">
         <v/>
       </c>
       <c r="E70">
-        <v>8602</v>
+        <v>6684</v>
       </c>
       <c r="F70" t="str">
         <v>Pendente</v>
@@ -2521,22 +2130,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>Antonio</v>
+        <v>Luiz Airton</v>
       </c>
       <c r="C71" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D71" t="str">
         <v/>
       </c>
       <c r="E71">
-        <v>1558</v>
+        <v>6684</v>
       </c>
       <c r="F71" t="str">
         <v>Pendente</v>
       </c>
       <c r="G71" t="str">
-        <v>19/04/2025</v>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -2544,7 +2153,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>Rafael Dutra</v>
+        <v>Angela</v>
       </c>
       <c r="C72" t="str">
         <v>Adulto</v>
@@ -2553,7 +2162,7 @@
         <v/>
       </c>
       <c r="E72">
-        <v>7947</v>
+        <v>9860</v>
       </c>
       <c r="F72" t="str">
         <v>Pendente</v>
@@ -2567,7 +2176,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>Hérica Marques</v>
+        <v>Alexandre</v>
       </c>
       <c r="C73" t="str">
         <v>Adulto</v>
@@ -2576,7 +2185,7 @@
         <v/>
       </c>
       <c r="E73">
-        <v>8284</v>
+        <v>9860</v>
       </c>
       <c r="F73" t="str">
         <v>Pendente</v>
@@ -2590,7 +2199,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>Thomas</v>
+        <v>Amanda</v>
       </c>
       <c r="C74" t="str">
         <v>Adulto</v>
@@ -2599,7 +2208,7 @@
         <v/>
       </c>
       <c r="E74">
-        <v>8284</v>
+        <v>1558</v>
       </c>
       <c r="F74" t="str">
         <v>Pendente</v>
@@ -2613,16 +2222,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>Gustavo</v>
+        <v>Giuliano</v>
       </c>
       <c r="C75" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D75" t="str">
         <v/>
       </c>
       <c r="E75">
-        <v>8284</v>
+        <v>1558</v>
       </c>
       <c r="F75" t="str">
         <v>Pendente</v>
@@ -2636,16 +2245,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>Guilherme</v>
+        <v>Natalia</v>
       </c>
       <c r="C76" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D76" t="str">
         <v/>
       </c>
       <c r="E76">
-        <v>8284</v>
+        <v>8602</v>
       </c>
       <c r="F76" t="str">
         <v>Pendente</v>
@@ -2659,16 +2268,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>Sofia</v>
+        <v>Guilherme Lobo</v>
       </c>
       <c r="C77" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D77" t="str">
         <v/>
       </c>
       <c r="E77">
-        <v>8284</v>
+        <v>8602</v>
       </c>
       <c r="F77" t="str">
         <v>Pendente</v>
@@ -2682,27 +2291,395 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
+        <v>Daniel</v>
+      </c>
+      <c r="C78" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78">
+        <v>5124</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Lorenzo</v>
+      </c>
+      <c r="C79" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79">
+        <v>4142</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Julia</v>
+      </c>
+      <c r="C80" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80">
+        <v>5124</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Julia Erling</v>
+      </c>
+      <c r="C81" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81">
+        <v>8778</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Theo</v>
+      </c>
+      <c r="C82" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82">
+        <v>8602</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Luisa Silva</v>
+      </c>
+      <c r="C83" t="str">
+        <v>CRIANCA (7 anos)</v>
+      </c>
+      <c r="D83">
+        <v>7</v>
+      </c>
+      <c r="E83">
+        <v>4417</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Antonio</v>
+      </c>
+      <c r="C84" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84">
+        <v>1558</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Benjamin Silva</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85">
+        <v>3261</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Benicio Silva</v>
+      </c>
+      <c r="C86" t="str">
+        <v>CRIANCA (10 anos)</v>
+      </c>
+      <c r="D86">
+        <v>10</v>
+      </c>
+      <c r="E86">
+        <v>3261</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Joaquim Silva</v>
+      </c>
+      <c r="C87" t="str">
+        <v>CRIANCA (8 anos)</v>
+      </c>
+      <c r="D87">
+        <v>8</v>
+      </c>
+      <c r="E87">
+        <v>3261</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Rafael Dutra</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88">
+        <v>7947</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Hérica Marques</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89">
+        <v>8284</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Thomas</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90">
+        <v>8284</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Gustavo</v>
+      </c>
+      <c r="C91" t="str">
+        <v>CRIANCA (8 anos)</v>
+      </c>
+      <c r="D91">
+        <v>8</v>
+      </c>
+      <c r="E91">
+        <v>8284</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Guilherme</v>
+      </c>
+      <c r="C92" t="str">
+        <v>CRIANCA (3 anos)</v>
+      </c>
+      <c r="D92">
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <v>8284</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Sofia</v>
+      </c>
+      <c r="C93" t="str">
+        <v>CRIANCA (1 anos)</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>8284</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
         <v>João Pedro Marçal</v>
       </c>
-      <c r="C78" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D78" t="str">
-        <v/>
-      </c>
-      <c r="E78">
+      <c r="C94" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94">
         <v>2036</v>
       </c>
-      <c r="F78" t="str">
-        <v>Pendente</v>
-      </c>
-      <c r="G78" t="str">
-        <v>04/05/2025</v>
+      <c r="F94" t="str">
+        <v>Pendente</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G94"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2736,25 +2713,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/graduation-api/convidados_confirmados.xlsx
+++ b/graduation-api/convidados_confirmados.xlsx
@@ -445,7 +445,7 @@
         <v>Confirmado</v>
       </c>
       <c r="G2" t="str">
-        <v>15/05/2025</v>
+        <v>15/06/2025</v>
       </c>
     </row>
     <row r="3">
@@ -462,13 +462,13 @@
         <v/>
       </c>
       <c r="E3">
-        <v>1240</v>
+        <v>2227</v>
       </c>
       <c r="F3" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G3" t="str">
-        <v>15/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -485,13 +485,13 @@
         <v/>
       </c>
       <c r="E4">
-        <v>1240</v>
+        <v>2227</v>
       </c>
       <c r="F4" t="str">
         <v>Confirmado</v>
       </c>
       <c r="G4" t="str">
-        <v>15/05/2025</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -503,10 +503,103 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:G4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>#</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nome</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Idade</v>
+      </c>
+      <c r="E1" t="str">
+        <v>CodigoConvite</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="G1" t="str">
+        <v>DataConfirmacao</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Natalia</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2">
+        <v>8602</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Recusado</v>
+      </c>
+      <c r="G2" t="str">
+        <v>19/05/2025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Guilherme Lobo</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Adulto</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3">
+        <v>8602</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Recusado</v>
+      </c>
+      <c r="G3" t="str">
+        <v>19/05/2025</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Theo</v>
+      </c>
+      <c r="C4" t="str">
+        <v>CRIANCA</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4">
+        <v>8602</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Recusado</v>
+      </c>
+      <c r="G4" t="str">
+        <v>19/05/2025</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -865,7 +958,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Cheila Machado</v>
+        <v>Cheila Jaques</v>
       </c>
       <c r="C16" t="str">
         <v>Adulto</v>
@@ -1601,7 +1694,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Ivan</v>
+        <v>Ivan Veloso</v>
       </c>
       <c r="C48" t="str">
         <v>Adulto</v>
@@ -1854,7 +1947,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>Gabriela</v>
+        <v>Gabriela Cruz</v>
       </c>
       <c r="C59" t="str">
         <v>Adulto</v>
@@ -1923,7 +2016,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Eduardo Kern</v>
+        <v>Henrique Demarchi</v>
       </c>
       <c r="C62" t="str">
         <v>Adulto</v>
@@ -1932,7 +2025,7 @@
         <v/>
       </c>
       <c r="E62">
-        <v>8504</v>
+        <v>2036</v>
       </c>
       <c r="F62" t="str">
         <v>Pendente</v>
@@ -1946,7 +2039,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Henrique Demarchi</v>
+        <v>Franciele de Leon</v>
       </c>
       <c r="C63" t="str">
         <v>Adulto</v>
@@ -1955,7 +2048,7 @@
         <v/>
       </c>
       <c r="E63">
-        <v>2036</v>
+        <v>8778</v>
       </c>
       <c r="F63" t="str">
         <v>Pendente</v>
@@ -1969,7 +2062,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>Franciele de Leon</v>
+        <v>Bruno Erling</v>
       </c>
       <c r="C64" t="str">
         <v>Adulto</v>
@@ -1992,7 +2085,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Bruno Erling</v>
+        <v>Sandriele de Leon</v>
       </c>
       <c r="C65" t="str">
         <v>Adulto</v>
@@ -2001,7 +2094,7 @@
         <v/>
       </c>
       <c r="E65">
-        <v>8778</v>
+        <v>4142</v>
       </c>
       <c r="F65" t="str">
         <v>Pendente</v>
@@ -2015,7 +2108,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Sandriele de Leon</v>
+        <v>Giuvanni Bagatini</v>
       </c>
       <c r="C66" t="str">
         <v>Adulto</v>
@@ -2038,7 +2131,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>Giuvanni Bagatini</v>
+        <v>Rochele de Leon</v>
       </c>
       <c r="C67" t="str">
         <v>Adulto</v>
@@ -2047,7 +2140,7 @@
         <v/>
       </c>
       <c r="E67">
-        <v>4142</v>
+        <v>3163</v>
       </c>
       <c r="F67" t="str">
         <v>Pendente</v>
@@ -2061,7 +2154,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>Rochele de Leon</v>
+        <v>Sandro Marques</v>
       </c>
       <c r="C68" t="str">
         <v>Adulto</v>
@@ -2084,7 +2177,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>Sandro Marques</v>
+        <v>Cleusa</v>
       </c>
       <c r="C69" t="str">
         <v>Adulto</v>
@@ -2093,7 +2186,7 @@
         <v/>
       </c>
       <c r="E69">
-        <v>3163</v>
+        <v>6684</v>
       </c>
       <c r="F69" t="str">
         <v>Pendente</v>
@@ -2107,7 +2200,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>Cleusa</v>
+        <v>Luiz Airton</v>
       </c>
       <c r="C70" t="str">
         <v>Adulto</v>
@@ -2130,7 +2223,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>Luiz Airton</v>
+        <v>Angela</v>
       </c>
       <c r="C71" t="str">
         <v>Adulto</v>
@@ -2139,7 +2232,7 @@
         <v/>
       </c>
       <c r="E71">
-        <v>6684</v>
+        <v>9860</v>
       </c>
       <c r="F71" t="str">
         <v>Pendente</v>
@@ -2153,7 +2246,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>Angela</v>
+        <v>Alexandre</v>
       </c>
       <c r="C72" t="str">
         <v>Adulto</v>
@@ -2176,7 +2269,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>Alexandre</v>
+        <v>Amanda</v>
       </c>
       <c r="C73" t="str">
         <v>Adulto</v>
@@ -2185,7 +2278,7 @@
         <v/>
       </c>
       <c r="E73">
-        <v>9860</v>
+        <v>1558</v>
       </c>
       <c r="F73" t="str">
         <v>Pendente</v>
@@ -2199,7 +2292,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>Amanda</v>
+        <v>Giuliano</v>
       </c>
       <c r="C74" t="str">
         <v>Adulto</v>
@@ -2222,16 +2315,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>Giuliano</v>
+        <v>Daniel</v>
       </c>
       <c r="C75" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D75" t="str">
-        <v/>
+        <v>CRIANCA (10 anos)</v>
+      </c>
+      <c r="D75">
+        <v>10</v>
       </c>
       <c r="E75">
-        <v>1558</v>
+        <v>5124</v>
       </c>
       <c r="F75" t="str">
         <v>Pendente</v>
@@ -2245,16 +2338,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>Natalia</v>
+        <v>Lorenzo</v>
       </c>
       <c r="C76" t="str">
-        <v>Adulto</v>
+        <v>CRIANCA</v>
       </c>
       <c r="D76" t="str">
         <v/>
       </c>
       <c r="E76">
-        <v>8602</v>
+        <v>4142</v>
       </c>
       <c r="F76" t="str">
         <v>Pendente</v>
@@ -2268,16 +2361,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>Guilherme Lobo</v>
+        <v>Julia</v>
       </c>
       <c r="C77" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D77" t="str">
-        <v/>
+        <v>CRIANCA (5 anos)</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
       </c>
       <c r="E77">
-        <v>8602</v>
+        <v>5124</v>
       </c>
       <c r="F77" t="str">
         <v>Pendente</v>
@@ -2291,7 +2384,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>Daniel</v>
+        <v>Julia</v>
       </c>
       <c r="C78" t="str">
         <v>CRIANCA</v>
@@ -2300,7 +2393,7 @@
         <v/>
       </c>
       <c r="E78">
-        <v>5124</v>
+        <v>8778</v>
       </c>
       <c r="F78" t="str">
         <v>Pendente</v>
@@ -2314,16 +2407,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>Lorenzo</v>
+        <v>Luisa Silva</v>
       </c>
       <c r="C79" t="str">
-        <v>CRIANCA</v>
-      </c>
-      <c r="D79" t="str">
-        <v/>
+        <v>CRIANCA (7 anos)</v>
+      </c>
+      <c r="D79">
+        <v>7</v>
       </c>
       <c r="E79">
-        <v>4142</v>
+        <v>4417</v>
       </c>
       <c r="F79" t="str">
         <v>Pendente</v>
@@ -2337,7 +2430,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>Julia</v>
+        <v>Antonio</v>
       </c>
       <c r="C80" t="str">
         <v>CRIANCA</v>
@@ -2346,7 +2439,7 @@
         <v/>
       </c>
       <c r="E80">
-        <v>5124</v>
+        <v>1558</v>
       </c>
       <c r="F80" t="str">
         <v>Pendente</v>
@@ -2360,16 +2453,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>Julia Erling</v>
+        <v>Benjamin Silva</v>
       </c>
       <c r="C81" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D81" t="str">
         <v/>
       </c>
       <c r="E81">
-        <v>8778</v>
+        <v>3261</v>
       </c>
       <c r="F81" t="str">
         <v>Pendente</v>
@@ -2383,16 +2476,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>Theo</v>
+        <v>Benicio Silva</v>
       </c>
       <c r="C82" t="str">
-        <v>CRIANCA</v>
-      </c>
-      <c r="D82" t="str">
-        <v/>
+        <v>CRIANCA (10 anos)</v>
+      </c>
+      <c r="D82">
+        <v>10</v>
       </c>
       <c r="E82">
-        <v>8602</v>
+        <v>3261</v>
       </c>
       <c r="F82" t="str">
         <v>Pendente</v>
@@ -2406,16 +2499,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>Luisa Silva</v>
+        <v>Joaquim Silva</v>
       </c>
       <c r="C83" t="str">
-        <v>CRIANCA (7 anos)</v>
+        <v>CRIANCA (8 anos)</v>
       </c>
       <c r="D83">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E83">
-        <v>4417</v>
+        <v>3261</v>
       </c>
       <c r="F83" t="str">
         <v>Pendente</v>
@@ -2429,16 +2522,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>Antonio</v>
+        <v>Rafael Dutra</v>
       </c>
       <c r="C84" t="str">
-        <v>CRIANCA</v>
+        <v>Adulto</v>
       </c>
       <c r="D84" t="str">
         <v/>
       </c>
       <c r="E84">
-        <v>1558</v>
+        <v>7947</v>
       </c>
       <c r="F84" t="str">
         <v>Pendente</v>
@@ -2452,7 +2545,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>Benjamin Silva</v>
+        <v>Hérica Marques</v>
       </c>
       <c r="C85" t="str">
         <v>Adulto</v>
@@ -2461,7 +2554,7 @@
         <v/>
       </c>
       <c r="E85">
-        <v>3261</v>
+        <v>8284</v>
       </c>
       <c r="F85" t="str">
         <v>Pendente</v>
@@ -2475,16 +2568,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>Benicio Silva</v>
+        <v>Thomas</v>
       </c>
       <c r="C86" t="str">
-        <v>CRIANCA (10 anos)</v>
-      </c>
-      <c r="D86">
-        <v>10</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
       </c>
       <c r="E86">
-        <v>3261</v>
+        <v>8284</v>
       </c>
       <c r="F86" t="str">
         <v>Pendente</v>
@@ -2498,7 +2591,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>Joaquim Silva</v>
+        <v>Gustavo</v>
       </c>
       <c r="C87" t="str">
         <v>CRIANCA (8 anos)</v>
@@ -2507,7 +2600,7 @@
         <v>8</v>
       </c>
       <c r="E87">
-        <v>3261</v>
+        <v>8284</v>
       </c>
       <c r="F87" t="str">
         <v>Pendente</v>
@@ -2521,16 +2614,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>Rafael Dutra</v>
+        <v>Guilherme</v>
       </c>
       <c r="C88" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D88" t="str">
-        <v/>
+        <v>CRIANCA (3 anos)</v>
+      </c>
+      <c r="D88">
+        <v>3</v>
       </c>
       <c r="E88">
-        <v>7947</v>
+        <v>8284</v>
       </c>
       <c r="F88" t="str">
         <v>Pendente</v>
@@ -2544,13 +2637,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>Hérica Marques</v>
+        <v>Sofia</v>
       </c>
       <c r="C89" t="str">
-        <v>Adulto</v>
-      </c>
-      <c r="D89" t="str">
-        <v/>
+        <v>CRIANCA (1 anos)</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
       </c>
       <c r="E89">
         <v>8284</v>
@@ -2567,7 +2660,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>Thomas</v>
+        <v>Nicollas Freitas</v>
       </c>
       <c r="C90" t="str">
         <v>Adulto</v>
@@ -2576,7 +2669,7 @@
         <v/>
       </c>
       <c r="E90">
-        <v>8284</v>
+        <v>4339</v>
       </c>
       <c r="F90" t="str">
         <v>Pendente</v>
@@ -2590,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>Gustavo</v>
+        <v>Ana Carolina</v>
       </c>
       <c r="C91" t="str">
-        <v>CRIANCA (8 anos)</v>
-      </c>
-      <c r="D91">
-        <v>8</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
       </c>
       <c r="E91">
-        <v>8284</v>
+        <v>8734</v>
       </c>
       <c r="F91" t="str">
         <v>Pendente</v>
@@ -2613,16 +2706,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>Guilherme</v>
+        <v>Rafaela Zappas</v>
       </c>
       <c r="C92" t="str">
-        <v>CRIANCA (3 anos)</v>
-      </c>
-      <c r="D92">
-        <v>3</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D92" t="str">
+        <v/>
       </c>
       <c r="E92">
-        <v>8284</v>
+        <v>8734</v>
       </c>
       <c r="F92" t="str">
         <v>Pendente</v>
@@ -2636,16 +2729,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>Sofia</v>
+        <v>César Augusto</v>
       </c>
       <c r="C93" t="str">
-        <v>CRIANCA (1 anos)</v>
-      </c>
-      <c r="D93">
-        <v>1</v>
+        <v>Adulto</v>
+      </c>
+      <c r="D93" t="str">
+        <v/>
       </c>
       <c r="E93">
-        <v>8284</v>
+        <v>8734</v>
       </c>
       <c r="F93" t="str">
         <v>Pendente</v>
@@ -2659,7 +2752,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>João Pedro Marçal</v>
+        <v>Ester</v>
       </c>
       <c r="C94" t="str">
         <v>Adulto</v>
@@ -2668,7 +2761,7 @@
         <v/>
       </c>
       <c r="E94">
-        <v>2036</v>
+        <v>8734</v>
       </c>
       <c r="F94" t="str">
         <v>Pendente</v>
@@ -2716,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>93</v>
